--- a/data/file/template_karyawan.xlsx
+++ b/data/file/template_karyawan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aryax punya\2026\KKA VAB\Aplikasi\imbalan-pasca-kerja-app\data\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B8343A-BDC6-44D0-8097-FF72F38F1B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7682ED-1848-4D15-9BD4-FF0FD00EAF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F13F3C63-F4E3-4D7D-949D-333584CBF9CF}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="214">
   <si>
     <t>KRY LAMA</t>
   </si>
@@ -278,6 +278,432 @@
   </si>
   <si>
     <t>selisih tersebut adalah karyawan yang masuk di tahun 2025 lalu resign di tahun yang sama</t>
+  </si>
+  <si>
+    <t>LUVITA NAZRIATUL AZIZAH</t>
+  </si>
+  <si>
+    <t>MUHAMAD SAIFIDIN</t>
+  </si>
+  <si>
+    <t>TATI MARYATI</t>
+  </si>
+  <si>
+    <t>MOCHAMMAD JHON MAYOR HASIBUAN</t>
+  </si>
+  <si>
+    <t>NURUL FADKHATUSSIYADAH</t>
+  </si>
+  <si>
+    <t>IDIEL ALFITRI SALSABILA</t>
+  </si>
+  <si>
+    <t>NUR AZIZAH APRIANI</t>
+  </si>
+  <si>
+    <t>AHMAD GHIFARI</t>
+  </si>
+  <si>
+    <t>JORDAN RUALEMBA</t>
+  </si>
+  <si>
+    <t>MOH FARIL</t>
+  </si>
+  <si>
+    <t>MUH DANDI</t>
+  </si>
+  <si>
+    <t>MUH.ARHAM MARDAYANSYAH</t>
+  </si>
+  <si>
+    <t>MUHAMAD FERDI</t>
+  </si>
+  <si>
+    <t>MUHAMMAD AZAN FADLY</t>
+  </si>
+  <si>
+    <t>SUPRIADI</t>
+  </si>
+  <si>
+    <t>YUSDAR</t>
+  </si>
+  <si>
+    <t>RISA NUR FAJRIATI</t>
+  </si>
+  <si>
+    <t>ANDRE</t>
+  </si>
+  <si>
+    <t>STEVAN MANGNGANDO</t>
+  </si>
+  <si>
+    <t>HERMIN CINO SAMBOLANGI</t>
+  </si>
+  <si>
+    <t>AKBAR</t>
+  </si>
+  <si>
+    <t>HERMAN A</t>
+  </si>
+  <si>
+    <t>IWALDI PATANGKO</t>
+  </si>
+  <si>
+    <t>ZETH SERU PAKIDING</t>
+  </si>
+  <si>
+    <t>ZULKIFLI</t>
+  </si>
+  <si>
+    <t>ADNAN</t>
+  </si>
+  <si>
+    <t>ANGGI RINALDI</t>
+  </si>
+  <si>
+    <t>IKRAM ARDIANSYAH</t>
+  </si>
+  <si>
+    <t>MISDAR ANUGRAH PUTRA</t>
+  </si>
+  <si>
+    <t>HISKIA TABI MENDA'</t>
+  </si>
+  <si>
+    <t>MAWAL FADLI</t>
+  </si>
+  <si>
+    <t>SYAWAL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>AKSAN AHMAD ALFA REZAL</t>
+  </si>
+  <si>
+    <t>ERIK SANDRA</t>
+  </si>
+  <si>
+    <t>IPAN ERIAN PUTRA MANGIDI</t>
+  </si>
+  <si>
+    <t>KHAIDER RAHMAWANGSA</t>
+  </si>
+  <si>
+    <t>MASLAN</t>
+  </si>
+  <si>
+    <t>MUH IBNU SUBAIR</t>
+  </si>
+  <si>
+    <t>MUH. RIZKY</t>
+  </si>
+  <si>
+    <t>MUHAMMAD AKBAR</t>
+  </si>
+  <si>
+    <t>MUHAMMAD SAIFUL</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ZADIL MUSTAMIN</t>
+  </si>
+  <si>
+    <t>VINCEN CHIAN LEE</t>
+  </si>
+  <si>
+    <t>FULVIA</t>
+  </si>
+  <si>
+    <t>MUH FAIZAL KILWOU</t>
+  </si>
+  <si>
+    <t>MUHAMMAD REZKI SALIM</t>
+  </si>
+  <si>
+    <t>ABD RAHIM</t>
+  </si>
+  <si>
+    <t>HENDRI RAMADHAN</t>
+  </si>
+  <si>
+    <t>ABDUL ROHIM</t>
+  </si>
+  <si>
+    <t>ALI AKBAR</t>
+  </si>
+  <si>
+    <t>ANSAR. , S.M</t>
+  </si>
+  <si>
+    <t>FEBRIANSYAH</t>
+  </si>
+  <si>
+    <t>IMAM TRI PUTRA S NAWAI</t>
+  </si>
+  <si>
+    <t>MATIUS SATOR</t>
+  </si>
+  <si>
+    <t>RIZAL HAKIM</t>
+  </si>
+  <si>
+    <t>IRMA ISYARA</t>
+  </si>
+  <si>
+    <t>ISLAMIA RANA</t>
+  </si>
+  <si>
+    <t>RESKI ANANDA</t>
+  </si>
+  <si>
+    <t>WA ODE SUKMAWATI</t>
+  </si>
+  <si>
+    <t>YUSRIL A. ZAKARIA</t>
+  </si>
+  <si>
+    <t>OKTAVIA NATASYA</t>
+  </si>
+  <si>
+    <t>SIMON SESA</t>
+  </si>
+  <si>
+    <t>SYAHRUL M.S.</t>
+  </si>
+  <si>
+    <t>APRISANTO ANTONIO GERU</t>
+  </si>
+  <si>
+    <t>ANDI CHAERIL AZWAR, S.H.</t>
+  </si>
+  <si>
+    <t>JUNARTO</t>
+  </si>
+  <si>
+    <t>AGUNG BUDJALEMBA</t>
+  </si>
+  <si>
+    <t>ARSAN</t>
+  </si>
+  <si>
+    <t>CHAERIL ARFANDA</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ASRIL</t>
+  </si>
+  <si>
+    <t>MUHAMMAD RIZKHY JUNI ARLANGGA</t>
+  </si>
+  <si>
+    <t>RAHMAT WAL HIDAYAT</t>
+  </si>
+  <si>
+    <t>SEPIN SITANGA'</t>
+  </si>
+  <si>
+    <t>SANDI</t>
+  </si>
+  <si>
+    <t>DERMAWAN</t>
+  </si>
+  <si>
+    <t>FEBRI JULIANDANA</t>
+  </si>
+  <si>
+    <t>RIYAN ARYO</t>
+  </si>
+  <si>
+    <t>SIAU MING</t>
+  </si>
+  <si>
+    <t>ARMADI</t>
+  </si>
+  <si>
+    <t>CORNELLIUS</t>
+  </si>
+  <si>
+    <t>DEDI</t>
+  </si>
+  <si>
+    <t>DENY JATMIKO</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>FRENKY PADONDAN</t>
+  </si>
+  <si>
+    <t>ISRA ANDI M.IQBAL</t>
+  </si>
+  <si>
+    <t>JODI RUSLI</t>
+  </si>
+  <si>
+    <t>MARWANDI PRATAMA PATIUNG</t>
+  </si>
+  <si>
+    <t>MUH RISWAN</t>
+  </si>
+  <si>
+    <t>NURMAN AMAL</t>
+  </si>
+  <si>
+    <t>PRAYOGA PUTRA</t>
+  </si>
+  <si>
+    <t>RIFALDI</t>
+  </si>
+  <si>
+    <t>ZUL FAJRI</t>
+  </si>
+  <si>
+    <t>FITRI</t>
+  </si>
+  <si>
+    <t>AGUNG</t>
+  </si>
+  <si>
+    <t>AKHMAL RIDWAN</t>
+  </si>
+  <si>
+    <t>ANDIKA</t>
+  </si>
+  <si>
+    <t>APRIANTO</t>
+  </si>
+  <si>
+    <t>DAWAM HABIBULLOH</t>
+  </si>
+  <si>
+    <t>HENDI PRADANA EKA SAKTI</t>
+  </si>
+  <si>
+    <t>PREDIANTO</t>
+  </si>
+  <si>
+    <t>RIYAN SAHKRUL</t>
+  </si>
+  <si>
+    <t>MAULANA FAJRI</t>
+  </si>
+  <si>
+    <t>NOSITO PASOANG</t>
+  </si>
+  <si>
+    <t>RAHMAD</t>
+  </si>
+  <si>
+    <t>TAUFIK HIDAYAT</t>
+  </si>
+  <si>
+    <t>ARIES NUR AFIANTO</t>
+  </si>
+  <si>
+    <t>ASHAR</t>
+  </si>
+  <si>
+    <t>FAUZAN ARMADI</t>
+  </si>
+  <si>
+    <t>HENDRIK TOMPINA</t>
+  </si>
+  <si>
+    <t>IRFANDI</t>
+  </si>
+  <si>
+    <t>WILTON FEDRIYANTO</t>
+  </si>
+  <si>
+    <t>GILBERT MILANO LINGGALO</t>
+  </si>
+  <si>
+    <t>SATRIO</t>
+  </si>
+  <si>
+    <t>HENDA YULI ARTA</t>
+  </si>
+  <si>
+    <t>SAPUTRA ABD KADIR</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ILHAM</t>
+  </si>
+  <si>
+    <t>AHMAD FADLY</t>
+  </si>
+  <si>
+    <t>FIRMANSYAH ADE PUTRA</t>
+  </si>
+  <si>
+    <t>PRASETIAWAN</t>
+  </si>
+  <si>
+    <t>REZA ARIZONA</t>
+  </si>
+  <si>
+    <t>MUH. WAHYUDI</t>
+  </si>
+  <si>
+    <t>MICHAEL CHIAN</t>
+  </si>
+  <si>
+    <t>JONATHAN JASON SEBASTIAN</t>
+  </si>
+  <si>
+    <t>ADIPUTRA S BOGODAD</t>
+  </si>
+  <si>
+    <t>CHAIRIL</t>
+  </si>
+  <si>
+    <t>I PUTU YOGA SUMADHY</t>
+  </si>
+  <si>
+    <t>MUH FAHMI</t>
+  </si>
+  <si>
+    <t>DEDI ISWANTO</t>
+  </si>
+  <si>
+    <t>ERIK ROSANDI</t>
+  </si>
+  <si>
+    <t>IDUL SAPUTRA</t>
+  </si>
+  <si>
+    <t>MEYDI SATRIAWAN</t>
+  </si>
+  <si>
+    <t>SAHRUL</t>
+  </si>
+  <si>
+    <t>WANDES PALULLUNGAN</t>
+  </si>
+  <si>
+    <t>ABDY DARMADI</t>
+  </si>
+  <si>
+    <t>AFANDI</t>
+  </si>
+  <si>
+    <t>HARI PRIYO UTOMO</t>
+  </si>
+  <si>
+    <t>NURATIKA ROSIDIN</t>
+  </si>
+  <si>
+    <t>DEDEN SAPUTRA</t>
+  </si>
+  <si>
+    <t>LAODE MUHAMAD KASRIN</t>
+  </si>
+  <si>
+    <t>M. TAKBIR .S</t>
+  </si>
+  <si>
+    <t>ASRAR</t>
   </si>
 </sst>
 </file>
@@ -3723,7 +4149,7 @@
       </c>
       <c r="F3" s="21">
         <f>COUNTIF(AB12:AB3000,"Baru ada di 2025")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="21"/>
       <c r="I3" s="22"/>
@@ -3781,7 +4207,7 @@
       </c>
       <c r="F5" s="21">
         <f>SUM(F2:F4)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="21"/>
       <c r="I5" s="15"/>
@@ -3810,7 +4236,7 @@
       </c>
       <c r="F6" s="21">
         <f>COUNT(B12:B2000)</f>
-        <v>3</v>
+        <v>176</v>
       </c>
       <c r="G6" s="21"/>
       <c r="I6" s="12"/>
@@ -3837,7 +4263,7 @@
       </c>
       <c r="F7" s="4">
         <f>F6-F5</f>
-        <v>-29</v>
+        <v>145</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>71</v>
@@ -3866,7 +4292,7 @@
       </c>
       <c r="F8" s="5">
         <f>COUNTIF(AG12:AG3000,"#N/A")</f>
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G8" s="5"/>
       <c r="I8" s="12"/>
@@ -4331,7 +4757,7 @@
         <v>EVA INDRIYANI</v>
       </c>
       <c r="AB12" s="50" t="str">
-        <f t="shared" ref="AB12:AB19" si="0">IF(NOT(ISNA(AA12)),"","Baru ada di 2025")</f>
+        <f t="shared" ref="AB12" si="0">IF(NOT(ISNA(AA12)),"","Baru ada di 2025")</f>
         <v/>
       </c>
       <c r="AC12" s="51" t="e">
@@ -4339,16 +4765,16 @@
         <v>#N/A</v>
       </c>
       <c r="AD12" s="51" t="str">
-        <f t="shared" ref="AD12:AD17" si="1">IF(ISNA(AC12),I12,"")</f>
+        <f t="shared" ref="AD12" si="1">IF(ISNA(AC12),I12,"")</f>
         <v>AGUNG GUNAWAN MAKMUR</v>
       </c>
       <c r="AE12" s="1"/>
       <c r="AF12" s="51" t="e">
-        <f t="shared" ref="AF12:AF17" si="2">IF(AD12="","",VLOOKUP(AD12,$Q$12:$Q$194,1,0))</f>
+        <f t="shared" ref="AF12" si="2">IF(AD12="","",VLOOKUP(AD12,$Q$12:$Q$194,1,0))</f>
         <v>#N/A</v>
       </c>
       <c r="AG12" s="1" t="e">
-        <f t="shared" ref="AG12:AG17" si="3">IF(AF12&lt;&gt;"","resign di 2025","")</f>
+        <f t="shared" ref="AG12" si="3">IF(AF12&lt;&gt;"","resign di 2025","")</f>
         <v>#N/A</v>
       </c>
       <c r="AI12" s="1" t="e">
@@ -4360,7 +4786,7 @@
         <v>#N/A</v>
       </c>
       <c r="AL12" s="1" t="str">
-        <f t="shared" ref="AL12:AL18" si="4">VLOOKUP(Q12,$I$12:$I$1000,1,0)</f>
+        <f t="shared" ref="AL12" si="4">VLOOKUP(Q12,$I$12:$I$1000,1,0)</f>
         <v>ALDIN</v>
       </c>
       <c r="AN12" s="1" t="str">
@@ -4370,23 +4796,23 @@
     </row>
     <row r="13" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>82400506</v>
+        <v>82401182</v>
       </c>
       <c r="B13" s="46">
-        <f t="shared" ref="B13:B14" si="5">B12+1</f>
+        <f t="shared" ref="B13:B76" si="5">B12+1</f>
         <v>2</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="41">
-        <v>35554</v>
-      </c>
-      <c r="E13" s="74">
-        <v>44779</v>
+      <c r="C13" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="37">
+        <v>34786</v>
+      </c>
+      <c r="E13" s="10">
+        <v>44980</v>
       </c>
       <c r="F13" s="38">
-        <v>5980000</v>
+        <v>4380000</v>
       </c>
       <c r="G13" s="38"/>
       <c r="H13" s="46">
@@ -4445,29 +4871,29 @@
       </c>
       <c r="Z13" s="47"/>
       <c r="AA13" s="49" t="e">
-        <f t="shared" ref="AA13:AA76" si="7">VLOOKUP(C13,$I$12:$I$994,1,0)</f>
+        <f t="shared" ref="AA13:AA14" si="7">VLOOKUP(C13,$I$12:$I$994,1,0)</f>
         <v>#N/A</v>
       </c>
       <c r="AB13" s="50" t="str">
-        <f t="shared" ref="AB13:AB76" si="8">IF(NOT(ISNA(AA13)),"","Baru ada di 2025")</f>
+        <f t="shared" ref="AB13:AB14" si="8">IF(NOT(ISNA(AA13)),"","Baru ada di 2025")</f>
         <v>Baru ada di 2025</v>
       </c>
-      <c r="AC13" s="51" t="e">
+      <c r="AC13" s="51" t="str">
         <f t="shared" ref="AC13:AC47" si="9">VLOOKUP(I13,$C$12:$C$994,1,0)</f>
-        <v>#N/A</v>
+        <v>ALMIRA NOPY VALENCIA</v>
       </c>
       <c r="AD13" s="51" t="str">
         <f t="shared" ref="AD13:AD47" si="10">IF(ISNA(AC13),I13,"")</f>
-        <v>ALMIRA NOPY VALENCIA</v>
+        <v/>
       </c>
       <c r="AE13" s="1"/>
-      <c r="AF13" s="51" t="e">
+      <c r="AF13" s="51" t="str">
         <f t="shared" ref="AF13:AF47" si="11">IF(AD13="","",VLOOKUP(AD13,$Q$12:$Q$194,1,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG13" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG13" s="1" t="str">
         <f t="shared" ref="AG13:AG47" si="12">IF(AF13&lt;&gt;"","resign di 2025","")</f>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI13" s="1" t="e">
         <f t="shared" ref="AI13:AI47" si="13">VLOOKUP(C13,$Q$12:$Q$994,1,0)</f>
@@ -4488,23 +4914,23 @@
     </row>
     <row r="14" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>87900152</v>
+        <v>82402325</v>
       </c>
       <c r="B14" s="46">
-        <f>B13+1</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="C14" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="40">
-        <v>34691</v>
-      </c>
-      <c r="E14" s="74">
-        <v>45852</v>
+      <c r="C14" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="37">
+        <v>36936</v>
+      </c>
+      <c r="E14" s="10">
+        <v>45320</v>
       </c>
       <c r="F14" s="38">
-        <v>4058000</v>
+        <v>4130000</v>
       </c>
       <c r="G14" s="38"/>
       <c r="H14" s="46">
@@ -4562,13 +4988,13 @@
         <v>46022</v>
       </c>
       <c r="Z14" s="47"/>
-      <c r="AA14" s="49" t="e">
+      <c r="AA14" s="49" t="str">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>ALMIRA NOPY VALENCIA</v>
       </c>
       <c r="AB14" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Baru ada di 2025</v>
+        <v/>
       </c>
       <c r="AC14" s="51" t="str">
         <f t="shared" si="9"/>
@@ -4605,11 +5031,25 @@
       </c>
     </row>
     <row r="15" spans="1:255" x14ac:dyDescent="0.3">
-      <c r="B15" s="46"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="38"/>
+      <c r="A15" s="1">
+        <v>82700071</v>
+      </c>
+      <c r="B15" s="46">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="37">
+        <v>34682</v>
+      </c>
+      <c r="E15" s="10">
+        <v>45403</v>
+      </c>
+      <c r="F15" s="38">
+        <v>4530000</v>
+      </c>
       <c r="G15" s="38"/>
       <c r="H15" s="46">
         <f t="shared" si="6"/>
@@ -4668,22 +5108,22 @@
       <c r="Z15" s="56"/>
       <c r="AA15" s="49"/>
       <c r="AB15" s="50"/>
-      <c r="AC15" s="51" t="e">
+      <c r="AC15" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>LADY VIOLA MAHARANI</v>
       </c>
       <c r="AD15" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>LADY VIOLA MAHARANI</v>
+        <v/>
       </c>
       <c r="AE15" s="1"/>
-      <c r="AF15" s="51" t="e">
+      <c r="AF15" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG15" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG15" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI15" s="1" t="e">
         <f t="shared" si="13"/>
@@ -4703,11 +5143,25 @@
       </c>
     </row>
     <row r="16" spans="1:255" x14ac:dyDescent="0.3">
-      <c r="B16" s="46"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="38"/>
+      <c r="A16" s="1">
+        <v>82402291</v>
+      </c>
+      <c r="B16" s="46">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="37">
+        <v>30839</v>
+      </c>
+      <c r="E16" s="10">
+        <v>45306</v>
+      </c>
+      <c r="F16" s="38">
+        <v>4130000</v>
+      </c>
       <c r="G16" s="38"/>
       <c r="H16" s="46">
         <f t="shared" si="6"/>
@@ -4766,22 +5220,22 @@
       <c r="Z16" s="47"/>
       <c r="AA16" s="49"/>
       <c r="AB16" s="50"/>
-      <c r="AC16" s="51" t="e">
+      <c r="AC16" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ELYP OKTAVIANUS</v>
       </c>
       <c r="AD16" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ELYP OKTAVIANUS</v>
+        <v/>
       </c>
       <c r="AE16" s="1"/>
-      <c r="AF16" s="51" t="e">
+      <c r="AF16" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG16" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG16" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI16" s="1" t="e">
         <f t="shared" si="13"/>
@@ -4800,11 +5254,26 @@
         <v>ANISA</v>
       </c>
     </row>
-    <row r="17" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B17" s="46"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="38"/>
+    <row r="17" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>82402711</v>
+      </c>
+      <c r="B17" s="46">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="37">
+        <v>36239</v>
+      </c>
+      <c r="E17" s="10">
+        <v>45436</v>
+      </c>
+      <c r="F17" s="38">
+        <v>4130000</v>
+      </c>
       <c r="G17" s="38"/>
       <c r="H17" s="46">
         <f t="shared" si="6"/>
@@ -4862,22 +5331,22 @@
       <c r="Z17" s="47"/>
       <c r="AA17" s="49"/>
       <c r="AB17" s="50"/>
-      <c r="AC17" s="51" t="e">
+      <c r="AC17" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>AKLAH HARSAB WUNGKO</v>
       </c>
       <c r="AD17" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>AKLAH HARSAB WUNGKO</v>
+        <v/>
       </c>
       <c r="AE17" s="1"/>
-      <c r="AF17" s="51" t="e">
+      <c r="AF17" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG17" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG17" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI17" s="1" t="e">
         <f t="shared" si="13"/>
@@ -4896,11 +5365,26 @@
         <v>WISNU ABD HOLIS</v>
       </c>
     </row>
-    <row r="18" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B18" s="46"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="38"/>
+    <row r="18" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>82402968</v>
+      </c>
+      <c r="B18" s="46">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="37">
+        <v>32077</v>
+      </c>
+      <c r="E18" s="10">
+        <v>45474</v>
+      </c>
+      <c r="F18" s="38">
+        <v>4130000</v>
+      </c>
       <c r="G18" s="38"/>
       <c r="H18" s="46">
         <f t="shared" si="6"/>
@@ -4937,22 +5421,22 @@
       <c r="Z18" s="61"/>
       <c r="AA18" s="49"/>
       <c r="AB18" s="50"/>
-      <c r="AC18" s="51" t="e">
+      <c r="AC18" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>NURUL FADKHATUSSIYADAH</v>
       </c>
       <c r="AD18" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>Nurul Fadkhatussiyadah</v>
+        <v/>
       </c>
       <c r="AE18" s="1"/>
-      <c r="AF18" s="51" t="e">
+      <c r="AF18" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG18" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG18" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI18" s="1" t="e">
         <f t="shared" si="13"/>
@@ -4971,11 +5455,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B19" s="46"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="38"/>
+    <row r="19" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>82403023</v>
+      </c>
+      <c r="B19" s="46">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="37">
+        <v>36974</v>
+      </c>
+      <c r="E19" s="10">
+        <v>45474</v>
+      </c>
+      <c r="F19" s="38">
+        <v>4230000</v>
+      </c>
       <c r="G19" s="38"/>
       <c r="H19" s="46">
         <f t="shared" si="6"/>
@@ -5012,22 +5511,22 @@
       <c r="Z19" s="61"/>
       <c r="AA19" s="49"/>
       <c r="AB19" s="50"/>
-      <c r="AC19" s="51" t="e">
+      <c r="AC19" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ARIFIAH MUFLIKHATI PUTRI</v>
       </c>
       <c r="AD19" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ARIFIAH MUFLIKHATI PUTRI</v>
+        <v/>
       </c>
       <c r="AE19" s="1"/>
-      <c r="AF19" s="51" t="e">
+      <c r="AF19" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG19" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG19" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI19" s="1" t="e">
         <f t="shared" si="13"/>
@@ -5046,11 +5545,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B20" s="46"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="38"/>
+    <row r="20" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>82403093</v>
+      </c>
+      <c r="B20" s="46">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="37">
+        <v>35106</v>
+      </c>
+      <c r="E20" s="10">
+        <v>45495</v>
+      </c>
+      <c r="F20" s="38">
+        <v>3500000</v>
+      </c>
       <c r="G20" s="38"/>
       <c r="H20" s="46">
         <f t="shared" si="6"/>
@@ -5121,11 +5635,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B21" s="46"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="38"/>
+    <row r="21" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>82403117</v>
+      </c>
+      <c r="B21" s="46">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="37">
+        <v>36591</v>
+      </c>
+      <c r="E21" s="10">
+        <v>45502</v>
+      </c>
+      <c r="F21" s="38">
+        <v>4130000</v>
+      </c>
       <c r="G21" s="38"/>
       <c r="H21" s="46">
         <f t="shared" si="6"/>
@@ -5196,11 +5725,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B22" s="46"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="38"/>
+    <row r="22" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>82403126</v>
+      </c>
+      <c r="B22" s="46">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="37">
+        <v>37068</v>
+      </c>
+      <c r="E22" s="10">
+        <v>45502</v>
+      </c>
+      <c r="F22" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G22" s="38"/>
       <c r="H22" s="46">
         <f t="shared" si="6"/>
@@ -5486,11 +6030,26 @@
       <c r="IT22" s="29"/>
       <c r="IU22" s="29"/>
     </row>
-    <row r="23" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B23" s="46"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="38"/>
+    <row r="23" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>82403146</v>
+      </c>
+      <c r="B23" s="46">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="37">
+        <v>38307</v>
+      </c>
+      <c r="E23" s="10">
+        <v>45509</v>
+      </c>
+      <c r="F23" s="38">
+        <v>4130000</v>
+      </c>
       <c r="G23" s="38"/>
       <c r="H23" s="46">
         <f t="shared" si="6"/>
@@ -5561,11 +6120,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B24" s="46"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="38"/>
+    <row r="24" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>82403282</v>
+      </c>
+      <c r="B24" s="46">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="37">
+        <v>36320</v>
+      </c>
+      <c r="E24" s="10">
+        <v>45532</v>
+      </c>
+      <c r="F24" s="38">
+        <v>4180000</v>
+      </c>
       <c r="G24" s="38"/>
       <c r="H24" s="46">
         <f t="shared" si="6"/>
@@ -5636,11 +6210,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B25" s="46"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="38"/>
+    <row r="25" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>82403284</v>
+      </c>
+      <c r="B25" s="46">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="37">
+        <v>37528</v>
+      </c>
+      <c r="E25" s="10">
+        <v>45532</v>
+      </c>
+      <c r="F25" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G25" s="38"/>
       <c r="H25" s="46">
         <f t="shared" si="6"/>
@@ -5677,22 +6266,22 @@
       <c r="Z25" s="61"/>
       <c r="AA25" s="49"/>
       <c r="AB25" s="50"/>
-      <c r="AC25" s="51" t="e">
+      <c r="AC25" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>MUHAMAD AMIN PUTRA SALIM</v>
       </c>
       <c r="AD25" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>MUHAMAD AMIN PUTRA SALIM</v>
+        <v/>
       </c>
       <c r="AE25" s="1"/>
-      <c r="AF25" s="51" t="e">
+      <c r="AF25" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG25" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG25" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI25" s="1" t="e">
         <f t="shared" si="13"/>
@@ -5711,11 +6300,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B26" s="46"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="38"/>
+    <row r="26" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>82403350</v>
+      </c>
+      <c r="B26" s="46">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="37">
+        <v>38456</v>
+      </c>
+      <c r="E26" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F26" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G26" s="38"/>
       <c r="H26" s="46">
         <f t="shared" si="6"/>
@@ -5752,22 +6356,22 @@
       <c r="Z26" s="61"/>
       <c r="AA26" s="49"/>
       <c r="AB26" s="50"/>
-      <c r="AC26" s="51" t="e">
+      <c r="AC26" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>RADEN</v>
       </c>
       <c r="AD26" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>RADEN</v>
+        <v/>
       </c>
       <c r="AE26" s="1"/>
-      <c r="AF26" s="51" t="e">
+      <c r="AF26" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG26" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG26" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI26" s="1" t="e">
         <f t="shared" si="13"/>
@@ -5786,11 +6390,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B27" s="46"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="38"/>
+    <row r="27" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>82403351</v>
+      </c>
+      <c r="B27" s="46">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="37">
+        <v>37411</v>
+      </c>
+      <c r="E27" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F27" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G27" s="38"/>
       <c r="H27" s="46">
         <f t="shared" si="6"/>
@@ -5827,22 +6446,22 @@
       <c r="Z27" s="61"/>
       <c r="AA27" s="49"/>
       <c r="AB27" s="50"/>
-      <c r="AC27" s="51" t="e">
+      <c r="AC27" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>MUH AKBAR</v>
       </c>
       <c r="AD27" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>MUH AKBAR</v>
+        <v/>
       </c>
       <c r="AE27" s="1"/>
-      <c r="AF27" s="51" t="e">
+      <c r="AF27" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG27" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG27" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI27" s="1" t="e">
         <f t="shared" si="13"/>
@@ -5861,11 +6480,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B28" s="46"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="38"/>
+    <row r="28" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>82403352</v>
+      </c>
+      <c r="B28" s="46">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="37">
+        <v>35110</v>
+      </c>
+      <c r="E28" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F28" s="38">
+        <v>4480000</v>
+      </c>
       <c r="G28" s="38"/>
       <c r="H28" s="46">
         <f t="shared" si="6"/>
@@ -5902,22 +6536,22 @@
       <c r="Z28" s="61"/>
       <c r="AA28" s="49"/>
       <c r="AB28" s="50"/>
-      <c r="AC28" s="51" t="e">
+      <c r="AC28" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ARI SYAH RIDAR</v>
       </c>
       <c r="AD28" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ARI SYAH RIDAR</v>
+        <v/>
       </c>
       <c r="AE28" s="1"/>
-      <c r="AF28" s="51" t="e">
+      <c r="AF28" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG28" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG28" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI28" s="1" t="e">
         <f t="shared" si="13"/>
@@ -5936,11 +6570,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B29" s="46"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="38"/>
+    <row r="29" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>82403353</v>
+      </c>
+      <c r="B29" s="46">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="37">
+        <v>37603</v>
+      </c>
+      <c r="E29" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F29" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G29" s="38"/>
       <c r="H29" s="46">
         <f t="shared" si="6"/>
@@ -5977,22 +6626,22 @@
       <c r="Z29" s="61"/>
       <c r="AA29" s="49"/>
       <c r="AB29" s="50"/>
-      <c r="AC29" s="51" t="e">
+      <c r="AC29" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>STEVEN TOMBI RA'PAK LANGI</v>
       </c>
       <c r="AD29" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>STEVEN TOMBI RA'PAK LANGI</v>
+        <v/>
       </c>
       <c r="AE29" s="1"/>
-      <c r="AF29" s="51" t="e">
+      <c r="AF29" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG29" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG29" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI29" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6011,11 +6660,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B30" s="46"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="38"/>
+    <row r="30" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>82403354</v>
+      </c>
+      <c r="B30" s="46">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="37">
+        <v>37956</v>
+      </c>
+      <c r="E30" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F30" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G30" s="38"/>
       <c r="H30" s="46">
         <f t="shared" si="6"/>
@@ -6052,22 +6716,22 @@
       <c r="Z30" s="61"/>
       <c r="AA30" s="49"/>
       <c r="AB30" s="50"/>
-      <c r="AC30" s="51" t="e">
+      <c r="AC30" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ALPEN DANGGULU</v>
       </c>
       <c r="AD30" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ALPEN DANGGULU</v>
+        <v/>
       </c>
       <c r="AE30" s="1"/>
-      <c r="AF30" s="51" t="e">
+      <c r="AF30" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG30" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG30" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI30" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6086,11 +6750,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B31" s="46"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="38"/>
+    <row r="31" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>82403355</v>
+      </c>
+      <c r="B31" s="46">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="37">
+        <v>37572</v>
+      </c>
+      <c r="E31" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F31" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G31" s="38"/>
       <c r="H31" s="46">
         <f t="shared" si="6"/>
@@ -6127,22 +6806,22 @@
       <c r="Z31" s="61"/>
       <c r="AA31" s="49"/>
       <c r="AB31" s="50"/>
-      <c r="AC31" s="51" t="e">
+      <c r="AC31" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ARIF</v>
       </c>
       <c r="AD31" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ARIF</v>
+        <v/>
       </c>
       <c r="AE31" s="1"/>
-      <c r="AF31" s="51" t="e">
+      <c r="AF31" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG31" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG31" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI31" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6161,11 +6840,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:255" x14ac:dyDescent="0.3">
-      <c r="B32" s="46"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="38"/>
+    <row r="32" spans="1:255" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>82403356</v>
+      </c>
+      <c r="B32" s="46">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="37">
+        <v>34699</v>
+      </c>
+      <c r="E32" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F32" s="38">
+        <v>4230000</v>
+      </c>
       <c r="G32" s="38"/>
       <c r="H32" s="46">
         <f t="shared" si="6"/>
@@ -6202,22 +6896,22 @@
       <c r="Z32" s="61"/>
       <c r="AA32" s="49"/>
       <c r="AB32" s="50"/>
-      <c r="AC32" s="51" t="e">
+      <c r="AC32" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ESRONI BABUNO</v>
       </c>
       <c r="AD32" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ESRONI BABUNO</v>
+        <v/>
       </c>
       <c r="AE32" s="1"/>
-      <c r="AF32" s="51" t="e">
+      <c r="AF32" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG32" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG32" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI32" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6236,11 +6930,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B33" s="46"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="38"/>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>82403357</v>
+      </c>
+      <c r="B33" s="46">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="37">
+        <v>36617</v>
+      </c>
+      <c r="E33" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F33" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G33" s="38"/>
       <c r="H33" s="46">
         <f t="shared" si="6"/>
@@ -6277,22 +6986,22 @@
       <c r="Z33" s="61"/>
       <c r="AA33" s="49"/>
       <c r="AB33" s="50"/>
-      <c r="AC33" s="51" t="e">
+      <c r="AC33" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>FIRMANSYAH</v>
       </c>
       <c r="AD33" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>FIRMANSYAH</v>
+        <v/>
       </c>
       <c r="AE33" s="1"/>
-      <c r="AF33" s="51" t="e">
+      <c r="AF33" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG33" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG33" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI33" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6311,11 +7020,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B34" s="46"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="38"/>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>82403358</v>
+      </c>
+      <c r="B34" s="46">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="37">
+        <v>37907</v>
+      </c>
+      <c r="E34" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F34" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G34" s="38"/>
       <c r="H34" s="46">
         <f t="shared" si="6"/>
@@ -6352,22 +7076,22 @@
       <c r="Z34" s="61"/>
       <c r="AA34" s="49"/>
       <c r="AB34" s="50"/>
-      <c r="AC34" s="51" t="e">
+      <c r="AC34" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>KEVIN MARCELINO METOLI</v>
       </c>
       <c r="AD34" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>KEVIN MARCELINO METOLI</v>
+        <v/>
       </c>
       <c r="AE34" s="1"/>
-      <c r="AF34" s="51" t="e">
+      <c r="AF34" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG34" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG34" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI34" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6386,11 +7110,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B35" s="46"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="38"/>
+    <row r="35" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>82403359</v>
+      </c>
+      <c r="B35" s="46">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35" s="37">
+        <v>36376</v>
+      </c>
+      <c r="E35" s="10">
+        <v>45548</v>
+      </c>
+      <c r="F35" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G35" s="38"/>
       <c r="H35" s="46">
         <f t="shared" si="6"/>
@@ -6428,22 +7167,22 @@
       <c r="Z35" s="61"/>
       <c r="AA35" s="49"/>
       <c r="AB35" s="50"/>
-      <c r="AC35" s="51" t="e">
+      <c r="AC35" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>MALIK</v>
       </c>
       <c r="AD35" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>MALIK</v>
+        <v/>
       </c>
       <c r="AE35" s="1"/>
-      <c r="AF35" s="51" t="e">
+      <c r="AF35" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG35" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG35" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI35" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6462,11 +7201,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B36" s="46"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="38"/>
+    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>82403360</v>
+      </c>
+      <c r="B36" s="46">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="37">
+        <v>37021</v>
+      </c>
+      <c r="E36" s="37">
+        <v>45548</v>
+      </c>
+      <c r="F36" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G36" s="38"/>
       <c r="H36" s="46">
         <f t="shared" si="6"/>
@@ -6504,22 +7258,22 @@
       <c r="Z36" s="61"/>
       <c r="AA36" s="49"/>
       <c r="AB36" s="50"/>
-      <c r="AC36" s="51" t="e">
+      <c r="AC36" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>RIFKA TOGON</v>
       </c>
       <c r="AD36" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>RIFKA TOGON</v>
+        <v/>
       </c>
       <c r="AE36" s="1"/>
-      <c r="AF36" s="51" t="e">
+      <c r="AF36" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG36" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG36" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI36" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6538,11 +7292,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B37" s="46"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="38"/>
+    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>82403387</v>
+      </c>
+      <c r="B37" s="46">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="37">
+        <v>38205</v>
+      </c>
+      <c r="E37" s="37">
+        <v>45556</v>
+      </c>
+      <c r="F37" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G37" s="38"/>
       <c r="H37" s="46">
         <f t="shared" si="6"/>
@@ -6580,22 +7349,22 @@
       <c r="Z37" s="61"/>
       <c r="AA37" s="49"/>
       <c r="AB37" s="50"/>
-      <c r="AC37" s="51" t="e">
+      <c r="AC37" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>RIZALDI</v>
       </c>
       <c r="AD37" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>RIZALDI</v>
+        <v/>
       </c>
       <c r="AE37" s="1"/>
-      <c r="AF37" s="51" t="e">
+      <c r="AF37" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG37" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG37" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI37" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6614,11 +7383,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B38" s="46"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="38"/>
+    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>82403388</v>
+      </c>
+      <c r="B38" s="46">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="37">
+        <v>37998</v>
+      </c>
+      <c r="E38" s="37">
+        <v>45556</v>
+      </c>
+      <c r="F38" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G38" s="38"/>
       <c r="H38" s="46">
         <f t="shared" si="6"/>
@@ -6690,11 +7474,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B39" s="46"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="38"/>
+    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>82403389</v>
+      </c>
+      <c r="B39" s="46">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="37">
+        <v>37205</v>
+      </c>
+      <c r="E39" s="37">
+        <v>45556</v>
+      </c>
+      <c r="F39" s="38">
+        <v>4230000</v>
+      </c>
       <c r="G39" s="38"/>
       <c r="H39" s="46">
         <f t="shared" si="6"/>
@@ -6732,22 +7531,22 @@
       <c r="Z39" s="61"/>
       <c r="AA39" s="49"/>
       <c r="AB39" s="50"/>
-      <c r="AC39" s="51" t="e">
+      <c r="AC39" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>AYU SEPTIA RIZKY RABBANA</v>
       </c>
       <c r="AD39" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>AYU SEPTIA RIZKY RABBANA</v>
+        <v/>
       </c>
       <c r="AE39" s="1"/>
-      <c r="AF39" s="51" t="e">
+      <c r="AF39" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG39" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG39" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI39" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6766,11 +7565,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B40" s="46"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="38"/>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>82403391</v>
+      </c>
+      <c r="B40" s="46">
+        <f t="shared" si="5"/>
+        <v>29</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="37">
+        <v>38410</v>
+      </c>
+      <c r="E40" s="37">
+        <v>45556</v>
+      </c>
+      <c r="F40" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G40" s="38"/>
       <c r="H40" s="46">
         <f t="shared" si="6"/>
@@ -6808,22 +7622,22 @@
       <c r="Z40" s="61"/>
       <c r="AA40" s="49"/>
       <c r="AB40" s="50"/>
-      <c r="AC40" s="51" t="e">
+      <c r="AC40" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>RENALDY FRANSISKUS TULENAN</v>
       </c>
       <c r="AD40" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>RENALDY FRANSISKUS TULENAN</v>
+        <v/>
       </c>
       <c r="AE40" s="1"/>
-      <c r="AF40" s="51" t="e">
+      <c r="AF40" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG40" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG40" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI40" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6842,11 +7656,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B41" s="46"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="38"/>
+    <row r="41" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>82403392</v>
+      </c>
+      <c r="B41" s="46">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="37">
+        <v>37750</v>
+      </c>
+      <c r="E41" s="37">
+        <v>45556</v>
+      </c>
+      <c r="F41" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G41" s="38"/>
       <c r="H41" s="46">
         <f t="shared" si="6"/>
@@ -6884,22 +7713,22 @@
       <c r="Z41" s="61"/>
       <c r="AA41" s="49"/>
       <c r="AB41" s="50"/>
-      <c r="AC41" s="51" t="e">
+      <c r="AC41" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ANDI SELVI</v>
       </c>
       <c r="AD41" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ANDI SELVI</v>
+        <v/>
       </c>
       <c r="AE41" s="1"/>
-      <c r="AF41" s="51" t="e">
+      <c r="AF41" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG41" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG41" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI41" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6918,11 +7747,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B42" s="46"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="38"/>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>82403394</v>
+      </c>
+      <c r="B42" s="46">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" s="37">
+        <v>36955</v>
+      </c>
+      <c r="E42" s="37">
+        <v>45556</v>
+      </c>
+      <c r="F42" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G42" s="38"/>
       <c r="H42" s="46">
         <f t="shared" si="6"/>
@@ -6960,22 +7804,22 @@
       <c r="Z42" s="61"/>
       <c r="AA42" s="49"/>
       <c r="AB42" s="50"/>
-      <c r="AC42" s="51" t="e">
+      <c r="AC42" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ALIYAH SAFIRA</v>
       </c>
       <c r="AD42" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ALIYAH SAFIRA</v>
+        <v/>
       </c>
       <c r="AE42" s="1"/>
-      <c r="AF42" s="51" t="e">
+      <c r="AF42" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG42" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG42" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI42" s="1" t="e">
         <f t="shared" si="13"/>
@@ -6994,11 +7838,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B43" s="46"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="38"/>
+    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>82403395</v>
+      </c>
+      <c r="B43" s="46">
+        <f t="shared" si="5"/>
+        <v>32</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="37">
+        <v>37561</v>
+      </c>
+      <c r="E43" s="37">
+        <v>45556</v>
+      </c>
+      <c r="F43" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G43" s="38"/>
       <c r="H43" s="46">
         <f t="shared" si="6"/>
@@ -7036,22 +7895,22 @@
       <c r="Z43" s="61"/>
       <c r="AA43" s="49"/>
       <c r="AB43" s="50"/>
-      <c r="AC43" s="51" t="e">
+      <c r="AC43" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ATMIN LAMBA</v>
       </c>
       <c r="AD43" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ATMIN LAMBA</v>
+        <v/>
       </c>
       <c r="AE43" s="1"/>
-      <c r="AF43" s="51" t="e">
+      <c r="AF43" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG43" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG43" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI43" s="1" t="e">
         <f t="shared" si="13"/>
@@ -7070,11 +7929,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B44" s="46"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="38"/>
+    <row r="44" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>82403396</v>
+      </c>
+      <c r="B44" s="46">
+        <f t="shared" si="5"/>
+        <v>33</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="37">
+        <v>37364</v>
+      </c>
+      <c r="E44" s="37">
+        <v>45556</v>
+      </c>
+      <c r="F44" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G44" s="38"/>
       <c r="H44" s="46">
         <f t="shared" si="6"/>
@@ -7112,22 +7986,22 @@
       <c r="Z44" s="61"/>
       <c r="AA44" s="49"/>
       <c r="AB44" s="50"/>
-      <c r="AC44" s="51" t="e">
+      <c r="AC44" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ISMAIL LABONE</v>
       </c>
       <c r="AD44" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ISMAIL LABONE</v>
+        <v/>
       </c>
       <c r="AE44" s="1"/>
-      <c r="AF44" s="51" t="e">
+      <c r="AF44" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG44" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG44" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI44" s="1" t="e">
         <f t="shared" si="13"/>
@@ -7146,11 +8020,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B45" s="46"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="38"/>
+    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>82403494</v>
+      </c>
+      <c r="B45" s="46">
+        <f t="shared" si="5"/>
+        <v>34</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="37">
+        <v>37005</v>
+      </c>
+      <c r="E45" s="37">
+        <v>45570</v>
+      </c>
+      <c r="F45" s="38">
+        <v>4130000</v>
+      </c>
       <c r="G45" s="38"/>
       <c r="H45" s="46">
         <f t="shared" si="6"/>
@@ -7187,22 +8076,22 @@
       <c r="Z45" s="61"/>
       <c r="AA45" s="49"/>
       <c r="AB45" s="50"/>
-      <c r="AC45" s="51" t="e">
+      <c r="AC45" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>MOH ABIL</v>
       </c>
       <c r="AD45" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>MOH ABIL</v>
+        <v/>
       </c>
       <c r="AE45" s="1"/>
-      <c r="AF45" s="51" t="e">
+      <c r="AF45" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG45" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG45" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI45" s="1" t="e">
         <f t="shared" si="13"/>
@@ -7221,11 +8110,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B46" s="46"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="38"/>
+    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>82403623</v>
+      </c>
+      <c r="B46" s="46">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="37">
+        <v>38101</v>
+      </c>
+      <c r="E46" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F46" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G46" s="38"/>
       <c r="H46" s="46">
         <f t="shared" si="6"/>
@@ -7263,22 +8167,22 @@
       <c r="Z46" s="61"/>
       <c r="AA46" s="49"/>
       <c r="AB46" s="50"/>
-      <c r="AC46" s="51" t="e">
+      <c r="AC46" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>ELSA TRIWANI DAUD</v>
       </c>
       <c r="AD46" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>ELSA TRIWANI DAUD</v>
+        <v/>
       </c>
       <c r="AE46" s="1"/>
-      <c r="AF46" s="51" t="e">
+      <c r="AF46" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG46" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG46" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI46" s="1" t="e">
         <f t="shared" si="13"/>
@@ -7297,11 +8201,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B47" s="46"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="38"/>
+    <row r="47" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>82403625</v>
+      </c>
+      <c r="B47" s="46">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="37">
+        <v>38008</v>
+      </c>
+      <c r="E47" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F47" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G47" s="38"/>
       <c r="H47" s="46">
         <f t="shared" si="6"/>
@@ -7339,22 +8258,22 @@
       <c r="Z47" s="61"/>
       <c r="AA47" s="49"/>
       <c r="AB47" s="50"/>
-      <c r="AC47" s="51" t="e">
+      <c r="AC47" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
+        <v>FARIT HIDAYAT</v>
       </c>
       <c r="AD47" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>FARIT HIDAYAT</v>
+        <v/>
       </c>
       <c r="AE47" s="1"/>
-      <c r="AF47" s="51" t="e">
+      <c r="AF47" s="51" t="str">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG47" s="1" t="e">
+        <v/>
+      </c>
+      <c r="AG47" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="AI47" s="1" t="e">
         <f t="shared" si="13"/>
@@ -7373,11 +8292,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B48" s="46"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="38"/>
+    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>82403626</v>
+      </c>
+      <c r="B48" s="46">
+        <f t="shared" si="5"/>
+        <v>37</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="37">
+        <v>38818</v>
+      </c>
+      <c r="E48" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F48" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G48" s="38"/>
       <c r="H48" s="46"/>
       <c r="I48" s="65"/>
@@ -7405,19 +8339,34 @@
       <c r="AE48" s="1"/>
       <c r="AF48" s="51"/>
       <c r="AI48" s="1" t="e">
-        <f t="shared" ref="AI13:AI70" si="18">VLOOKUP(C48,$Q$12:$Q$994,1,0)</f>
+        <f t="shared" ref="AI48:AI70" si="18">VLOOKUP(C48,$Q$12:$Q$994,1,0)</f>
         <v>#N/A</v>
       </c>
       <c r="AJ48" s="11" t="e">
-        <f t="shared" ref="AJ13:AJ70" si="19">IF(AI48&lt;&gt;"","ada di data resign tapi masih aktif","")</f>
+        <f t="shared" ref="AJ48:AJ70" si="19">IF(AI48&lt;&gt;"","ada di data resign tapi masih aktif","")</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B49" s="46"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="38"/>
+    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>82403627</v>
+      </c>
+      <c r="B49" s="46">
+        <f t="shared" si="5"/>
+        <v>38</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="37">
+        <v>38675</v>
+      </c>
+      <c r="E49" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F49" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G49" s="38"/>
       <c r="H49" s="46"/>
       <c r="I49" s="65"/>
@@ -7453,11 +8402,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="50" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B50" s="46"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="73"/>
+    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>82403628</v>
+      </c>
+      <c r="B50" s="46">
+        <f t="shared" si="5"/>
+        <v>39</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" s="37">
+        <v>36554</v>
+      </c>
+      <c r="E50" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F50" s="73">
+        <v>4030000</v>
+      </c>
       <c r="G50" s="73"/>
       <c r="H50" s="46"/>
       <c r="I50" s="39"/>
@@ -7493,11 +8457,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B51" s="46"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="38"/>
+    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>82403629</v>
+      </c>
+      <c r="B51" s="46">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" s="37">
+        <v>38602</v>
+      </c>
+      <c r="E51" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F51" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G51" s="38"/>
       <c r="H51" s="46"/>
       <c r="I51" s="1"/>
@@ -7533,11 +8512,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="52" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B52" s="46"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="38"/>
+    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>82403630</v>
+      </c>
+      <c r="B52" s="46">
+        <f t="shared" si="5"/>
+        <v>41</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D52" s="37">
+        <v>38691</v>
+      </c>
+      <c r="E52" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F52" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G52" s="38"/>
       <c r="H52" s="46"/>
       <c r="I52" s="65"/>
@@ -7573,11 +8567,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="53" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B53" s="46"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="38"/>
+    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>82403631</v>
+      </c>
+      <c r="B53" s="46">
+        <f t="shared" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D53" s="37">
+        <v>38828</v>
+      </c>
+      <c r="E53" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F53" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G53" s="38"/>
       <c r="H53" s="46"/>
       <c r="I53" s="65"/>
@@ -7612,11 +8621,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="54" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B54" s="46"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="38"/>
+    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>82403633</v>
+      </c>
+      <c r="B54" s="46">
+        <f t="shared" si="5"/>
+        <v>43</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="37">
+        <v>34844</v>
+      </c>
+      <c r="E54" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F54" s="38">
+        <v>4330000</v>
+      </c>
       <c r="G54" s="38"/>
       <c r="H54" s="46"/>
       <c r="I54" s="65"/>
@@ -7651,11 +8675,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="55" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B55" s="46"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="38"/>
+    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>82403634</v>
+      </c>
+      <c r="B55" s="46">
+        <f t="shared" si="5"/>
+        <v>44</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="37">
+        <v>38488</v>
+      </c>
+      <c r="E55" s="37">
+        <v>45601</v>
+      </c>
+      <c r="F55" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G55" s="38"/>
       <c r="H55" s="46"/>
       <c r="I55" s="39"/>
@@ -7690,11 +8729,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B56" s="46"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="38"/>
+    <row r="56" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>82403642</v>
+      </c>
+      <c r="B56" s="46">
+        <f t="shared" si="5"/>
+        <v>45</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D56" s="37">
+        <v>37308</v>
+      </c>
+      <c r="E56" s="37">
+        <v>45608</v>
+      </c>
+      <c r="F56" s="38">
+        <v>4130000</v>
+      </c>
       <c r="G56" s="38"/>
       <c r="H56" s="46"/>
       <c r="I56" s="39"/>
@@ -7729,11 +8783,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="57" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B57" s="46"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="38"/>
+    <row r="57" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>82403647</v>
+      </c>
+      <c r="B57" s="46">
+        <f t="shared" si="5"/>
+        <v>46</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D57" s="37">
+        <v>36928</v>
+      </c>
+      <c r="E57" s="37">
+        <v>45612</v>
+      </c>
+      <c r="F57" s="38">
+        <v>4230000</v>
+      </c>
       <c r="G57" s="38"/>
       <c r="H57" s="46"/>
       <c r="I57" s="39"/>
@@ -7768,11 +8837,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="58" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B58" s="46"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="38"/>
+    <row r="58" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>82403650</v>
+      </c>
+      <c r="B58" s="46">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" s="37">
+        <v>38681</v>
+      </c>
+      <c r="E58" s="37">
+        <v>45612</v>
+      </c>
+      <c r="F58" s="38">
+        <v>4030000</v>
+      </c>
       <c r="G58" s="38"/>
       <c r="H58" s="46"/>
       <c r="I58" s="65"/>
@@ -7807,11 +8891,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="59" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B59" s="46"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="38"/>
+    <row r="59" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>82404070</v>
+      </c>
+      <c r="B59" s="46">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="37">
+        <v>37374</v>
+      </c>
+      <c r="E59" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F59" s="38">
+        <v>4058000</v>
+      </c>
       <c r="G59" s="38"/>
       <c r="H59" s="46"/>
       <c r="I59" s="65"/>
@@ -7845,11 +8944,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="60" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B60" s="46"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="38"/>
+    <row r="60" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>82404094</v>
+      </c>
+      <c r="B60" s="46">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" s="37">
+        <v>37299</v>
+      </c>
+      <c r="E60" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F60" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G60" s="38"/>
       <c r="H60" s="46"/>
       <c r="I60" s="65"/>
@@ -7883,11 +8997,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="61" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B61" s="46"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="38"/>
+    <row r="61" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>82404095</v>
+      </c>
+      <c r="B61" s="46">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" s="37">
+        <v>34711</v>
+      </c>
+      <c r="E61" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F61" s="38">
+        <v>4158000</v>
+      </c>
       <c r="G61" s="38"/>
       <c r="H61" s="46"/>
       <c r="I61" s="65"/>
@@ -7921,11 +9050,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="62" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B62" s="46"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="38"/>
+    <row r="62" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>82404096</v>
+      </c>
+      <c r="B62" s="46">
+        <f t="shared" si="5"/>
+        <v>51</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" s="37">
+        <v>38751</v>
+      </c>
+      <c r="E62" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F62" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G62" s="38"/>
       <c r="H62" s="46"/>
       <c r="I62" s="65"/>
@@ -7959,11 +9103,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B63" s="46"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="38"/>
+    <row r="63" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>82404098</v>
+      </c>
+      <c r="B63" s="46">
+        <f t="shared" si="5"/>
+        <v>52</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D63" s="37">
+        <v>37214</v>
+      </c>
+      <c r="E63" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F63" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G63" s="38"/>
       <c r="H63" s="46"/>
       <c r="I63" s="39"/>
@@ -7997,11 +9156,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="64" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B64" s="46"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="38"/>
+    <row r="64" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>82404099</v>
+      </c>
+      <c r="B64" s="46">
+        <f t="shared" si="5"/>
+        <v>53</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" s="37">
+        <v>37075</v>
+      </c>
+      <c r="E64" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F64" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G64" s="38"/>
       <c r="H64" s="46"/>
       <c r="I64" s="65"/>
@@ -8035,11 +9209,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B65" s="46"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="38"/>
+    <row r="65" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>82404100</v>
+      </c>
+      <c r="B65" s="46">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D65" s="37">
+        <v>37367</v>
+      </c>
+      <c r="E65" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F65" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G65" s="38"/>
       <c r="H65" s="46"/>
       <c r="I65" s="65"/>
@@ -8073,11 +9262,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B66" s="46"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="38"/>
+    <row r="66" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>82404101</v>
+      </c>
+      <c r="B66" s="46">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D66" s="37">
+        <v>37836</v>
+      </c>
+      <c r="E66" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F66" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G66" s="38"/>
       <c r="H66" s="46"/>
       <c r="I66" s="65"/>
@@ -8111,11 +9315,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B67" s="46"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="38"/>
+    <row r="67" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>82404102</v>
+      </c>
+      <c r="B67" s="46">
+        <f t="shared" si="5"/>
+        <v>56</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D67" s="37">
+        <v>37809</v>
+      </c>
+      <c r="E67" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F67" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G67" s="38"/>
       <c r="H67" s="46"/>
       <c r="I67" s="65"/>
@@ -8149,11 +9368,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B68" s="46"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="38"/>
+    <row r="68" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>82404103</v>
+      </c>
+      <c r="B68" s="46">
+        <f t="shared" si="5"/>
+        <v>57</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" s="37">
+        <v>37394</v>
+      </c>
+      <c r="E68" s="37">
+        <v>45689</v>
+      </c>
+      <c r="F68" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G68" s="38"/>
       <c r="H68" s="46"/>
       <c r="I68" s="39"/>
@@ -8187,11 +9421,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B69" s="46"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="38"/>
+    <row r="69" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>82404147</v>
+      </c>
+      <c r="B69" s="46">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D69" s="37">
+        <v>36276</v>
+      </c>
+      <c r="E69" s="37">
+        <v>45701</v>
+      </c>
+      <c r="F69" s="38">
+        <v>4158000</v>
+      </c>
       <c r="G69" s="38"/>
       <c r="H69" s="46"/>
       <c r="I69" s="65"/>
@@ -8225,12 +9474,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B70" s="46"/>
-      <c r="C70" s="55"/>
-      <c r="D70" s="41"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="38"/>
+    <row r="70" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>82404148</v>
+      </c>
+      <c r="B70" s="46">
+        <f t="shared" si="5"/>
+        <v>59</v>
+      </c>
+      <c r="C70" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D70" s="41">
+        <v>37345</v>
+      </c>
+      <c r="E70" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F70" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G70" s="38"/>
       <c r="H70" s="46"/>
       <c r="I70" s="65"/>
@@ -8264,12 +9527,26 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B71" s="46"/>
-      <c r="C71" s="55"/>
-      <c r="D71" s="41"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="38"/>
+    <row r="71" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>82404149</v>
+      </c>
+      <c r="B71" s="46">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="C71" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="D71" s="41">
+        <v>39032</v>
+      </c>
+      <c r="E71" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F71" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G71" s="38"/>
       <c r="H71" s="46"/>
       <c r="I71" s="65"/>
@@ -8295,12 +9572,26 @@
       <c r="AE71" s="1"/>
       <c r="AF71" s="51"/>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B72" s="46"/>
-      <c r="C72" s="55"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="38"/>
+    <row r="72" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>82404150</v>
+      </c>
+      <c r="B72" s="46">
+        <f t="shared" si="5"/>
+        <v>61</v>
+      </c>
+      <c r="C72" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D72" s="41">
+        <v>38469</v>
+      </c>
+      <c r="E72" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F72" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G72" s="38"/>
       <c r="H72" s="46"/>
       <c r="I72" s="65"/>
@@ -8326,12 +9617,26 @@
       <c r="AE72" s="1"/>
       <c r="AF72" s="51"/>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B73" s="46"/>
-      <c r="C73" s="55"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="38"/>
+    <row r="73" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>82404151</v>
+      </c>
+      <c r="B73" s="46">
+        <f t="shared" si="5"/>
+        <v>62</v>
+      </c>
+      <c r="C73" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" s="41">
+        <v>38757</v>
+      </c>
+      <c r="E73" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F73" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G73" s="38"/>
       <c r="H73" s="46"/>
       <c r="I73" s="65"/>
@@ -8357,12 +9662,26 @@
       <c r="AE73" s="1"/>
       <c r="AF73" s="51"/>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B74" s="46"/>
-      <c r="C74" s="36"/>
-      <c r="D74" s="40"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="38"/>
+    <row r="74" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>82404152</v>
+      </c>
+      <c r="B74" s="46">
+        <f t="shared" si="5"/>
+        <v>63</v>
+      </c>
+      <c r="C74" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D74" s="40">
+        <v>38223</v>
+      </c>
+      <c r="E74" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F74" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G74" s="38"/>
       <c r="H74" s="46"/>
       <c r="I74" s="65"/>
@@ -8388,12 +9707,26 @@
       <c r="AE74" s="1"/>
       <c r="AF74" s="51"/>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B75" s="46"/>
-      <c r="C75" s="55"/>
-      <c r="D75" s="41"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="38"/>
+    <row r="75" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>82404153</v>
+      </c>
+      <c r="B75" s="46">
+        <f t="shared" si="5"/>
+        <v>64</v>
+      </c>
+      <c r="C75" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="41">
+        <v>38127</v>
+      </c>
+      <c r="E75" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F75" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G75" s="38"/>
       <c r="H75" s="46"/>
       <c r="I75" s="65"/>
@@ -8419,12 +9752,26 @@
       <c r="AE75" s="1"/>
       <c r="AF75" s="51"/>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B76" s="46"/>
-      <c r="C76" s="55"/>
-      <c r="D76" s="41"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="38"/>
+    <row r="76" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>82404154</v>
+      </c>
+      <c r="B76" s="46">
+        <f t="shared" si="5"/>
+        <v>65</v>
+      </c>
+      <c r="C76" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="D76" s="41">
+        <v>36907</v>
+      </c>
+      <c r="E76" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F76" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G76" s="38"/>
       <c r="H76" s="46"/>
       <c r="I76" s="65"/>
@@ -8450,12 +9797,26 @@
       <c r="AE76" s="1"/>
       <c r="AF76" s="51"/>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B77" s="46"/>
-      <c r="C77" s="55"/>
-      <c r="D77" s="41"/>
-      <c r="E77" s="74"/>
-      <c r="F77" s="38"/>
+    <row r="77" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>82404155</v>
+      </c>
+      <c r="B77" s="46">
+        <f t="shared" ref="B77:B140" si="20">B76+1</f>
+        <v>66</v>
+      </c>
+      <c r="C77" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="D77" s="41">
+        <v>38879</v>
+      </c>
+      <c r="E77" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F77" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G77" s="38"/>
       <c r="H77" s="46"/>
       <c r="I77" s="65"/>
@@ -8481,12 +9842,26 @@
       <c r="AE77" s="1"/>
       <c r="AF77" s="51"/>
     </row>
-    <row r="78" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B78" s="46"/>
-      <c r="C78" s="55"/>
-      <c r="D78" s="41"/>
-      <c r="E78" s="74"/>
-      <c r="F78" s="38"/>
+    <row r="78" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>82404156</v>
+      </c>
+      <c r="B78" s="46">
+        <f t="shared" si="20"/>
+        <v>67</v>
+      </c>
+      <c r="C78" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D78" s="41">
+        <v>38561</v>
+      </c>
+      <c r="E78" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F78" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G78" s="38"/>
       <c r="H78" s="46"/>
       <c r="I78" s="65"/>
@@ -8512,12 +9887,26 @@
       <c r="AE78" s="1"/>
       <c r="AF78" s="51"/>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B79" s="46"/>
-      <c r="C79" s="55"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="74"/>
-      <c r="F79" s="38"/>
+    <row r="79" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>82404157</v>
+      </c>
+      <c r="B79" s="46">
+        <f t="shared" si="20"/>
+        <v>68</v>
+      </c>
+      <c r="C79" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D79" s="41">
+        <v>34695</v>
+      </c>
+      <c r="E79" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F79" s="38">
+        <v>4258000</v>
+      </c>
       <c r="G79" s="38"/>
       <c r="H79" s="46"/>
       <c r="I79" s="65"/>
@@ -8543,12 +9932,26 @@
       <c r="AE79" s="1"/>
       <c r="AF79" s="51"/>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.3">
-      <c r="B80" s="46"/>
-      <c r="C80" s="55"/>
-      <c r="D80" s="41"/>
-      <c r="E80" s="74"/>
-      <c r="F80" s="38"/>
+    <row r="80" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>82404158</v>
+      </c>
+      <c r="B80" s="46">
+        <f t="shared" si="20"/>
+        <v>69</v>
+      </c>
+      <c r="C80" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D80" s="41">
+        <v>38506</v>
+      </c>
+      <c r="E80" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F80" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G80" s="38"/>
       <c r="H80" s="46"/>
       <c r="I80" s="65"/>
@@ -8574,12 +9977,26 @@
       <c r="AE80" s="1"/>
       <c r="AF80" s="51"/>
     </row>
-    <row r="81" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B81" s="46"/>
-      <c r="C81" s="36"/>
-      <c r="D81" s="40"/>
-      <c r="E81" s="74"/>
-      <c r="F81" s="38"/>
+    <row r="81" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>82404159</v>
+      </c>
+      <c r="B81" s="46">
+        <f t="shared" si="20"/>
+        <v>70</v>
+      </c>
+      <c r="C81" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="D81" s="40">
+        <v>37291</v>
+      </c>
+      <c r="E81" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F81" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G81" s="38"/>
       <c r="H81" s="46"/>
       <c r="I81" s="65"/>
@@ -8605,12 +10022,26 @@
       <c r="AE81" s="1"/>
       <c r="AF81" s="51"/>
     </row>
-    <row r="82" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B82" s="46"/>
-      <c r="C82" s="36"/>
-      <c r="D82" s="40"/>
-      <c r="E82" s="74"/>
-      <c r="F82" s="38"/>
+    <row r="82" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>82404160</v>
+      </c>
+      <c r="B82" s="46">
+        <f t="shared" si="20"/>
+        <v>71</v>
+      </c>
+      <c r="C82" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" s="40">
+        <v>37187</v>
+      </c>
+      <c r="E82" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F82" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G82" s="38"/>
       <c r="H82" s="46"/>
       <c r="I82" s="65"/>
@@ -8636,12 +10067,26 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="51"/>
     </row>
-    <row r="83" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B83" s="46"/>
-      <c r="C83" s="55"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="74"/>
-      <c r="F83" s="38"/>
+    <row r="83" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>82404161</v>
+      </c>
+      <c r="B83" s="46">
+        <f t="shared" si="20"/>
+        <v>72</v>
+      </c>
+      <c r="C83" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D83" s="41">
+        <v>38635</v>
+      </c>
+      <c r="E83" s="74">
+        <v>45701</v>
+      </c>
+      <c r="F83" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G83" s="38"/>
       <c r="H83" s="46"/>
       <c r="I83" s="65"/>
@@ -8667,12 +10112,26 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="51"/>
     </row>
-    <row r="84" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B84" s="46"/>
-      <c r="C84" s="55"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="74"/>
-      <c r="F84" s="38"/>
+    <row r="84" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>82404254</v>
+      </c>
+      <c r="B84" s="46">
+        <f t="shared" si="20"/>
+        <v>73</v>
+      </c>
+      <c r="C84" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="D84" s="41">
+        <v>36795</v>
+      </c>
+      <c r="E84" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F84" s="38">
+        <v>4058000</v>
+      </c>
       <c r="G84" s="38"/>
       <c r="H84" s="46"/>
       <c r="I84" s="65"/>
@@ -8698,12 +10157,26 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="51"/>
     </row>
-    <row r="85" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B85" s="46"/>
-      <c r="C85" s="55"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="74"/>
-      <c r="F85" s="38"/>
+    <row r="85" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>82404284</v>
+      </c>
+      <c r="B85" s="46">
+        <f t="shared" si="20"/>
+        <v>74</v>
+      </c>
+      <c r="C85" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="D85" s="41">
+        <v>36564</v>
+      </c>
+      <c r="E85" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F85" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G85" s="38"/>
       <c r="H85" s="46"/>
       <c r="I85" s="65"/>
@@ -8729,12 +10202,26 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="51"/>
     </row>
-    <row r="86" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B86" s="46"/>
-      <c r="C86" s="55"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="74"/>
-      <c r="F86" s="38"/>
+    <row r="86" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>82404285</v>
+      </c>
+      <c r="B86" s="46">
+        <f t="shared" si="20"/>
+        <v>75</v>
+      </c>
+      <c r="C86" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D86" s="41">
+        <v>37752</v>
+      </c>
+      <c r="E86" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F86" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G86" s="38"/>
       <c r="H86" s="46"/>
       <c r="I86" s="65"/>
@@ -8760,12 +10247,26 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="51"/>
     </row>
-    <row r="87" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B87" s="46"/>
-      <c r="C87" s="55"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="74"/>
-      <c r="F87" s="38"/>
+    <row r="87" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>82404340</v>
+      </c>
+      <c r="B87" s="46">
+        <f t="shared" si="20"/>
+        <v>76</v>
+      </c>
+      <c r="C87" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="D87" s="41">
+        <v>35097</v>
+      </c>
+      <c r="E87" s="74">
+        <v>45722</v>
+      </c>
+      <c r="F87" s="38">
+        <v>4258000</v>
+      </c>
       <c r="G87" s="38"/>
       <c r="H87" s="46"/>
       <c r="I87" s="65"/>
@@ -8791,12 +10292,26 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="51"/>
     </row>
-    <row r="88" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B88" s="46"/>
-      <c r="C88" s="55"/>
-      <c r="D88" s="41"/>
-      <c r="E88" s="74"/>
-      <c r="F88" s="38"/>
+    <row r="88" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>82404341</v>
+      </c>
+      <c r="B88" s="46">
+        <f t="shared" si="20"/>
+        <v>77</v>
+      </c>
+      <c r="C88" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="D88" s="41">
+        <v>36173</v>
+      </c>
+      <c r="E88" s="74">
+        <v>45722</v>
+      </c>
+      <c r="F88" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G88" s="38"/>
       <c r="H88" s="46"/>
       <c r="I88" s="65"/>
@@ -8822,12 +10337,26 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="51"/>
     </row>
-    <row r="89" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B89" s="46"/>
-      <c r="C89" s="55"/>
-      <c r="D89" s="41"/>
-      <c r="E89" s="74"/>
-      <c r="F89" s="38"/>
+    <row r="89" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>82404287</v>
+      </c>
+      <c r="B89" s="46">
+        <f t="shared" si="20"/>
+        <v>78</v>
+      </c>
+      <c r="C89" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="D89" s="41">
+        <v>36703</v>
+      </c>
+      <c r="E89" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F89" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G89" s="38"/>
       <c r="H89" s="46"/>
       <c r="I89" s="65"/>
@@ -8853,12 +10382,26 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="51"/>
     </row>
-    <row r="90" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B90" s="46"/>
-      <c r="C90" s="55"/>
-      <c r="D90" s="41"/>
-      <c r="E90" s="74"/>
-      <c r="F90" s="38"/>
+    <row r="90" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>82404288</v>
+      </c>
+      <c r="B90" s="46">
+        <f t="shared" si="20"/>
+        <v>79</v>
+      </c>
+      <c r="C90" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="D90" s="41">
+        <v>37198</v>
+      </c>
+      <c r="E90" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F90" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G90" s="38"/>
       <c r="H90" s="46"/>
       <c r="I90" s="65"/>
@@ -8884,12 +10427,26 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="51"/>
     </row>
-    <row r="91" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B91" s="46"/>
-      <c r="C91" s="55"/>
-      <c r="D91" s="41"/>
-      <c r="E91" s="74"/>
-      <c r="F91" s="38"/>
+    <row r="91" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>82404289</v>
+      </c>
+      <c r="B91" s="46">
+        <f t="shared" si="20"/>
+        <v>80</v>
+      </c>
+      <c r="C91" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D91" s="41">
+        <v>37517</v>
+      </c>
+      <c r="E91" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F91" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G91" s="38"/>
       <c r="H91" s="46"/>
       <c r="I91" s="65"/>
@@ -8915,12 +10472,26 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="51"/>
     </row>
-    <row r="92" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B92" s="46"/>
-      <c r="C92" s="55"/>
-      <c r="D92" s="41"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="38"/>
+    <row r="92" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>82404290</v>
+      </c>
+      <c r="B92" s="46">
+        <f t="shared" si="20"/>
+        <v>81</v>
+      </c>
+      <c r="C92" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="D92" s="41">
+        <v>36930</v>
+      </c>
+      <c r="E92" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F92" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G92" s="38"/>
       <c r="H92" s="46"/>
       <c r="I92" s="65"/>
@@ -8946,12 +10517,26 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="51"/>
     </row>
-    <row r="93" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B93" s="46"/>
-      <c r="C93" s="55"/>
-      <c r="D93" s="41"/>
-      <c r="E93" s="74"/>
-      <c r="F93" s="38"/>
+    <row r="93" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>82404291</v>
+      </c>
+      <c r="B93" s="46">
+        <f t="shared" si="20"/>
+        <v>82</v>
+      </c>
+      <c r="C93" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="D93" s="41">
+        <v>36254</v>
+      </c>
+      <c r="E93" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F93" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G93" s="38"/>
       <c r="H93" s="46"/>
       <c r="I93" s="65"/>
@@ -8977,12 +10562,26 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="51"/>
     </row>
-    <row r="94" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B94" s="46"/>
-      <c r="C94" s="55"/>
-      <c r="D94" s="41"/>
-      <c r="E94" s="74"/>
-      <c r="F94" s="38"/>
+    <row r="94" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>82404292</v>
+      </c>
+      <c r="B94" s="46">
+        <f t="shared" si="20"/>
+        <v>83</v>
+      </c>
+      <c r="C94" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="D94" s="41">
+        <v>36504</v>
+      </c>
+      <c r="E94" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F94" s="38">
+        <v>4108000</v>
+      </c>
       <c r="G94" s="38"/>
       <c r="H94" s="46"/>
       <c r="I94" s="65"/>
@@ -9008,12 +10607,26 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="51"/>
     </row>
-    <row r="95" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B95" s="46"/>
-      <c r="C95" s="55"/>
-      <c r="D95" s="41"/>
-      <c r="E95" s="74"/>
-      <c r="F95" s="38"/>
+    <row r="95" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>82404293</v>
+      </c>
+      <c r="B95" s="46">
+        <f t="shared" si="20"/>
+        <v>84</v>
+      </c>
+      <c r="C95" s="55" t="s">
+        <v>127</v>
+      </c>
+      <c r="D95" s="41">
+        <v>36350</v>
+      </c>
+      <c r="E95" s="74">
+        <v>45716</v>
+      </c>
+      <c r="F95" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G95" s="38"/>
       <c r="H95" s="46"/>
       <c r="I95" s="65"/>
@@ -9039,12 +10652,26 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="51"/>
     </row>
-    <row r="96" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B96" s="46"/>
-      <c r="C96" s="55"/>
-      <c r="D96" s="41"/>
-      <c r="E96" s="74"/>
-      <c r="F96" s="38"/>
+    <row r="96" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>82404451</v>
+      </c>
+      <c r="B96" s="46">
+        <f t="shared" si="20"/>
+        <v>85</v>
+      </c>
+      <c r="C96" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D96" s="41">
+        <v>37391</v>
+      </c>
+      <c r="E96" s="74">
+        <v>45737</v>
+      </c>
+      <c r="F96" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G96" s="38"/>
       <c r="H96" s="46"/>
       <c r="I96" s="65"/>
@@ -9070,12 +10697,26 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="51"/>
     </row>
-    <row r="97" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B97" s="46"/>
-      <c r="C97" s="55"/>
-      <c r="D97" s="41"/>
-      <c r="E97" s="74"/>
-      <c r="F97" s="38"/>
+    <row r="97" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>82404452</v>
+      </c>
+      <c r="B97" s="46">
+        <f t="shared" si="20"/>
+        <v>86</v>
+      </c>
+      <c r="C97" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="D97" s="41">
+        <v>37445</v>
+      </c>
+      <c r="E97" s="74">
+        <v>45737</v>
+      </c>
+      <c r="F97" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G97" s="38"/>
       <c r="H97" s="46"/>
       <c r="I97" s="65"/>
@@ -9101,12 +10742,26 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="51"/>
     </row>
-    <row r="98" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B98" s="46"/>
-      <c r="C98" s="55"/>
-      <c r="D98" s="41"/>
-      <c r="E98" s="74"/>
-      <c r="F98" s="38"/>
+    <row r="98" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>82404453</v>
+      </c>
+      <c r="B98" s="46">
+        <f t="shared" si="20"/>
+        <v>87</v>
+      </c>
+      <c r="C98" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="D98" s="41">
+        <v>37611</v>
+      </c>
+      <c r="E98" s="74">
+        <v>45737</v>
+      </c>
+      <c r="F98" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G98" s="38"/>
       <c r="H98" s="46"/>
       <c r="I98" s="65"/>
@@ -9132,12 +10787,26 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="51"/>
     </row>
-    <row r="99" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B99" s="46"/>
-      <c r="C99" s="55"/>
-      <c r="D99" s="41"/>
-      <c r="E99" s="74"/>
-      <c r="F99" s="38"/>
+    <row r="99" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>82404454</v>
+      </c>
+      <c r="B99" s="46">
+        <f t="shared" si="20"/>
+        <v>88</v>
+      </c>
+      <c r="C99" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="D99" s="41">
+        <v>36196</v>
+      </c>
+      <c r="E99" s="74">
+        <v>45737</v>
+      </c>
+      <c r="F99" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G99" s="38"/>
       <c r="H99" s="46"/>
       <c r="I99" s="65"/>
@@ -9163,12 +10832,26 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="51"/>
     </row>
-    <row r="100" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B100" s="46"/>
-      <c r="C100" s="36"/>
-      <c r="D100" s="40"/>
-      <c r="E100" s="74"/>
-      <c r="F100" s="38"/>
+    <row r="100" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>82404456</v>
+      </c>
+      <c r="B100" s="46">
+        <f t="shared" si="20"/>
+        <v>89</v>
+      </c>
+      <c r="C100" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="D100" s="40">
+        <v>36833</v>
+      </c>
+      <c r="E100" s="74">
+        <v>45737</v>
+      </c>
+      <c r="F100" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G100" s="38"/>
       <c r="H100" s="46"/>
       <c r="I100" s="65"/>
@@ -9194,12 +10877,26 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="51"/>
     </row>
-    <row r="101" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B101" s="46"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="40"/>
-      <c r="E101" s="74"/>
-      <c r="F101" s="38"/>
+    <row r="101" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>82404487</v>
+      </c>
+      <c r="B101" s="46">
+        <f t="shared" si="20"/>
+        <v>90</v>
+      </c>
+      <c r="C101" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D101" s="40">
+        <v>39021</v>
+      </c>
+      <c r="E101" s="74">
+        <v>45744</v>
+      </c>
+      <c r="F101" s="38">
+        <v>4058000</v>
+      </c>
       <c r="G101" s="38"/>
       <c r="H101" s="46"/>
       <c r="I101" s="65"/>
@@ -9225,12 +10922,26 @@
       <c r="AE101" s="1"/>
       <c r="AF101" s="51"/>
     </row>
-    <row r="102" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B102" s="46"/>
-      <c r="C102" s="55"/>
-      <c r="D102" s="41"/>
-      <c r="E102" s="74"/>
-      <c r="F102" s="38"/>
+    <row r="102" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>82404546</v>
+      </c>
+      <c r="B102" s="46">
+        <f t="shared" si="20"/>
+        <v>91</v>
+      </c>
+      <c r="C102" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="D102" s="41">
+        <v>34891</v>
+      </c>
+      <c r="E102" s="74">
+        <v>45744</v>
+      </c>
+      <c r="F102" s="38">
+        <v>3988000</v>
+      </c>
       <c r="G102" s="38"/>
       <c r="H102" s="46"/>
       <c r="I102" s="65"/>
@@ -9256,12 +10967,26 @@
       <c r="AE102" s="1"/>
       <c r="AF102" s="51"/>
     </row>
-    <row r="103" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B103" s="46"/>
-      <c r="C103" s="55"/>
-      <c r="D103" s="41"/>
-      <c r="E103" s="74"/>
-      <c r="F103" s="38"/>
+    <row r="103" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>82404547</v>
+      </c>
+      <c r="B103" s="46">
+        <f t="shared" si="20"/>
+        <v>92</v>
+      </c>
+      <c r="C103" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="D103" s="41">
+        <v>37703</v>
+      </c>
+      <c r="E103" s="74">
+        <v>45744</v>
+      </c>
+      <c r="F103" s="38">
+        <v>3388000</v>
+      </c>
       <c r="G103" s="38"/>
       <c r="H103" s="46"/>
       <c r="I103" s="65"/>
@@ -9287,12 +11012,26 @@
       <c r="AE103" s="1"/>
       <c r="AF103" s="51"/>
     </row>
-    <row r="104" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B104" s="46"/>
-      <c r="C104" s="55"/>
-      <c r="D104" s="41"/>
-      <c r="E104" s="74"/>
-      <c r="F104" s="38"/>
+    <row r="104" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>82404653</v>
+      </c>
+      <c r="B104" s="46">
+        <f t="shared" si="20"/>
+        <v>93</v>
+      </c>
+      <c r="C104" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="D104" s="41">
+        <v>34085</v>
+      </c>
+      <c r="E104" s="74">
+        <v>45744</v>
+      </c>
+      <c r="F104" s="38">
+        <v>4158000</v>
+      </c>
       <c r="G104" s="38"/>
       <c r="H104" s="46"/>
       <c r="I104" s="65"/>
@@ -9318,12 +11057,26 @@
       <c r="AE104" s="1"/>
       <c r="AF104" s="51"/>
     </row>
-    <row r="105" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B105" s="46"/>
-      <c r="C105" s="55"/>
-      <c r="D105" s="41"/>
-      <c r="E105" s="74"/>
-      <c r="F105" s="38"/>
+    <row r="105" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>82404705</v>
+      </c>
+      <c r="B105" s="46">
+        <f t="shared" si="20"/>
+        <v>94</v>
+      </c>
+      <c r="C105" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="D105" s="41">
+        <v>34910</v>
+      </c>
+      <c r="E105" s="74">
+        <v>45761</v>
+      </c>
+      <c r="F105" s="38">
+        <v>4188000</v>
+      </c>
       <c r="G105" s="38"/>
       <c r="H105" s="46"/>
       <c r="I105" s="65"/>
@@ -9349,12 +11102,26 @@
       <c r="AE105" s="1"/>
       <c r="AF105" s="51"/>
     </row>
-    <row r="106" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B106" s="46"/>
-      <c r="C106" s="55"/>
-      <c r="D106" s="41"/>
-      <c r="E106" s="74"/>
-      <c r="F106" s="38"/>
+    <row r="106" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>87900001</v>
+      </c>
+      <c r="B106" s="46">
+        <f t="shared" si="20"/>
+        <v>95</v>
+      </c>
+      <c r="C106" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="D106" s="41">
+        <v>36679</v>
+      </c>
+      <c r="E106" s="74">
+        <v>45768</v>
+      </c>
+      <c r="F106" s="38">
+        <v>4058000</v>
+      </c>
       <c r="G106" s="38"/>
       <c r="H106" s="46"/>
       <c r="I106" s="65"/>
@@ -9380,12 +11147,26 @@
       <c r="AE106" s="1"/>
       <c r="AF106" s="51"/>
     </row>
-    <row r="107" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B107" s="46"/>
-      <c r="C107" s="55"/>
-      <c r="D107" s="41"/>
-      <c r="E107" s="74"/>
-      <c r="F107" s="38"/>
+    <row r="107" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>87900002</v>
+      </c>
+      <c r="B107" s="46">
+        <f t="shared" si="20"/>
+        <v>96</v>
+      </c>
+      <c r="C107" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D107" s="41">
+        <v>36719</v>
+      </c>
+      <c r="E107" s="74">
+        <v>45768</v>
+      </c>
+      <c r="F107" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G107" s="38"/>
       <c r="H107" s="46"/>
       <c r="I107" s="65"/>
@@ -9411,12 +11192,26 @@
       <c r="AE107" s="1"/>
       <c r="AF107" s="51"/>
     </row>
-    <row r="108" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B108" s="46"/>
-      <c r="C108" s="55"/>
-      <c r="D108" s="41"/>
-      <c r="E108" s="74"/>
-      <c r="F108" s="38"/>
+    <row r="108" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>87900003</v>
+      </c>
+      <c r="B108" s="46">
+        <f t="shared" si="20"/>
+        <v>97</v>
+      </c>
+      <c r="C108" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="D108" s="41">
+        <v>38200</v>
+      </c>
+      <c r="E108" s="74">
+        <v>45768</v>
+      </c>
+      <c r="F108" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G108" s="38"/>
       <c r="H108" s="46"/>
       <c r="I108" s="65"/>
@@ -9442,12 +11237,26 @@
       <c r="AE108" s="1"/>
       <c r="AF108" s="51"/>
     </row>
-    <row r="109" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B109" s="46"/>
-      <c r="C109" s="55"/>
-      <c r="D109" s="41"/>
-      <c r="E109" s="74"/>
-      <c r="F109" s="38"/>
+    <row r="109" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>87900004</v>
+      </c>
+      <c r="B109" s="46">
+        <f t="shared" si="20"/>
+        <v>98</v>
+      </c>
+      <c r="C109" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="D109" s="41">
+        <v>31963</v>
+      </c>
+      <c r="E109" s="74">
+        <v>45768</v>
+      </c>
+      <c r="F109" s="38">
+        <v>4158000</v>
+      </c>
       <c r="G109" s="38"/>
       <c r="H109" s="46"/>
       <c r="I109" s="65"/>
@@ -9473,12 +11282,26 @@
       <c r="AE109" s="1"/>
       <c r="AF109" s="51"/>
     </row>
-    <row r="110" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B110" s="46"/>
-      <c r="C110" s="55"/>
-      <c r="D110" s="41"/>
-      <c r="E110" s="74"/>
-      <c r="F110" s="38"/>
+    <row r="110" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>87900005</v>
+      </c>
+      <c r="B110" s="46">
+        <f t="shared" si="20"/>
+        <v>99</v>
+      </c>
+      <c r="C110" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="D110" s="41">
+        <v>36789</v>
+      </c>
+      <c r="E110" s="74">
+        <v>45768</v>
+      </c>
+      <c r="F110" s="38">
+        <v>3988000</v>
+      </c>
       <c r="G110" s="38"/>
       <c r="H110" s="46"/>
       <c r="I110" s="65"/>
@@ -9504,12 +11327,26 @@
       <c r="AE110" s="1"/>
       <c r="AF110" s="51"/>
     </row>
-    <row r="111" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B111" s="46"/>
-      <c r="C111" s="55"/>
-      <c r="D111" s="41"/>
-      <c r="E111" s="74"/>
-      <c r="F111" s="38"/>
+    <row r="111" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>87900009</v>
+      </c>
+      <c r="B111" s="46">
+        <f t="shared" si="20"/>
+        <v>100</v>
+      </c>
+      <c r="C111" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="D111" s="41">
+        <v>36551</v>
+      </c>
+      <c r="E111" s="74">
+        <v>45768</v>
+      </c>
+      <c r="F111" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G111" s="38"/>
       <c r="H111" s="46"/>
       <c r="I111" s="65"/>
@@ -9535,12 +11372,26 @@
       <c r="AE111" s="1"/>
       <c r="AF111" s="51"/>
     </row>
-    <row r="112" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B112" s="46"/>
-      <c r="C112" s="55"/>
-      <c r="D112" s="41"/>
-      <c r="E112" s="74"/>
-      <c r="F112" s="38"/>
+    <row r="112" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>87900010</v>
+      </c>
+      <c r="B112" s="46">
+        <f t="shared" si="20"/>
+        <v>101</v>
+      </c>
+      <c r="C112" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="D112" s="41">
+        <v>38529</v>
+      </c>
+      <c r="E112" s="74">
+        <v>45768</v>
+      </c>
+      <c r="F112" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G112" s="38"/>
       <c r="H112" s="46"/>
       <c r="I112" s="65"/>
@@ -9566,12 +11417,26 @@
       <c r="AE112" s="1"/>
       <c r="AF112" s="51"/>
     </row>
-    <row r="113" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B113" s="46"/>
-      <c r="C113" s="55"/>
-      <c r="D113" s="41"/>
-      <c r="E113" s="74"/>
-      <c r="F113" s="38"/>
+    <row r="113" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>87900011</v>
+      </c>
+      <c r="B113" s="46">
+        <f t="shared" si="20"/>
+        <v>102</v>
+      </c>
+      <c r="C113" s="55" t="s">
+        <v>144</v>
+      </c>
+      <c r="D113" s="41">
+        <v>38315</v>
+      </c>
+      <c r="E113" s="74">
+        <v>45768</v>
+      </c>
+      <c r="F113" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G113" s="38"/>
       <c r="H113" s="46"/>
       <c r="I113" s="65"/>
@@ -9597,12 +11462,26 @@
       <c r="AE113" s="1"/>
       <c r="AF113" s="51"/>
     </row>
-    <row r="114" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B114" s="46"/>
-      <c r="C114" s="55"/>
-      <c r="D114" s="41"/>
-      <c r="E114" s="74"/>
-      <c r="F114" s="38"/>
+    <row r="114" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>87900012</v>
+      </c>
+      <c r="B114" s="46">
+        <f t="shared" si="20"/>
+        <v>103</v>
+      </c>
+      <c r="C114" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="D114" s="41">
+        <v>38610</v>
+      </c>
+      <c r="E114" s="74">
+        <v>45768</v>
+      </c>
+      <c r="F114" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G114" s="38"/>
       <c r="H114" s="46"/>
       <c r="I114" s="65"/>
@@ -9628,11 +11507,26 @@
       <c r="AE114" s="1"/>
       <c r="AF114" s="51"/>
     </row>
-    <row r="115" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B115" s="46"/>
-      <c r="D115" s="37"/>
-      <c r="E115" s="37"/>
-      <c r="F115" s="77"/>
+    <row r="115" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>87900013</v>
+      </c>
+      <c r="B115" s="46">
+        <f t="shared" si="20"/>
+        <v>104</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D115" s="37">
+        <v>37883</v>
+      </c>
+      <c r="E115" s="37">
+        <v>45775</v>
+      </c>
+      <c r="F115" s="77">
+        <v>4058000</v>
+      </c>
       <c r="G115" s="77"/>
       <c r="H115" s="46"/>
       <c r="I115" s="65"/>
@@ -9658,11 +11552,26 @@
       <c r="AE115" s="1"/>
       <c r="AF115" s="51"/>
     </row>
-    <row r="116" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B116" s="46"/>
-      <c r="D116" s="37"/>
-      <c r="E116" s="37"/>
-      <c r="F116" s="77"/>
+    <row r="116" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>87900014</v>
+      </c>
+      <c r="B116" s="46">
+        <f t="shared" si="20"/>
+        <v>105</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D116" s="37">
+        <v>37176</v>
+      </c>
+      <c r="E116" s="37">
+        <v>45775</v>
+      </c>
+      <c r="F116" s="77">
+        <v>3958000</v>
+      </c>
       <c r="G116" s="77"/>
       <c r="H116" s="46"/>
       <c r="I116" s="65"/>
@@ -9688,11 +11597,26 @@
       <c r="AE116" s="1"/>
       <c r="AF116" s="51"/>
     </row>
-    <row r="117" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B117" s="46"/>
-      <c r="D117" s="37"/>
-      <c r="E117" s="37"/>
-      <c r="F117" s="77"/>
+    <row r="117" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>87900017</v>
+      </c>
+      <c r="B117" s="46">
+        <f t="shared" si="20"/>
+        <v>106</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D117" s="37">
+        <v>37351</v>
+      </c>
+      <c r="E117" s="37">
+        <v>45782</v>
+      </c>
+      <c r="F117" s="77">
+        <v>3958000</v>
+      </c>
       <c r="G117" s="77"/>
       <c r="H117" s="46"/>
       <c r="I117" s="65"/>
@@ -9718,12 +11642,26 @@
       <c r="AE117" s="1"/>
       <c r="AF117" s="51"/>
     </row>
-    <row r="118" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B118" s="46"/>
-      <c r="C118" s="55"/>
-      <c r="D118" s="41"/>
-      <c r="E118" s="74"/>
-      <c r="F118" s="38"/>
+    <row r="118" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>87900018</v>
+      </c>
+      <c r="B118" s="46">
+        <f t="shared" si="20"/>
+        <v>107</v>
+      </c>
+      <c r="C118" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="D118" s="41">
+        <v>38753</v>
+      </c>
+      <c r="E118" s="74">
+        <v>45782</v>
+      </c>
+      <c r="F118" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G118" s="38"/>
       <c r="H118" s="46"/>
       <c r="I118" s="65"/>
@@ -9749,12 +11687,26 @@
       <c r="AE118" s="1"/>
       <c r="AF118" s="51"/>
     </row>
-    <row r="119" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B119" s="46"/>
-      <c r="C119" s="55"/>
-      <c r="D119" s="41"/>
-      <c r="E119" s="74"/>
-      <c r="F119" s="38"/>
+    <row r="119" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>87900021</v>
+      </c>
+      <c r="B119" s="46">
+        <f t="shared" si="20"/>
+        <v>108</v>
+      </c>
+      <c r="C119" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="D119" s="41">
+        <v>34173</v>
+      </c>
+      <c r="E119" s="74">
+        <v>45782</v>
+      </c>
+      <c r="F119" s="38">
+        <v>4158000</v>
+      </c>
       <c r="G119" s="38"/>
       <c r="H119" s="46"/>
       <c r="I119" s="65"/>
@@ -9780,12 +11732,26 @@
       <c r="AE119" s="1"/>
       <c r="AF119" s="51"/>
     </row>
-    <row r="120" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B120" s="46"/>
-      <c r="C120" s="55"/>
-      <c r="D120" s="41"/>
-      <c r="E120" s="74"/>
-      <c r="F120" s="38"/>
+    <row r="120" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>87900022</v>
+      </c>
+      <c r="B120" s="46">
+        <f t="shared" si="20"/>
+        <v>109</v>
+      </c>
+      <c r="C120" s="55" t="s">
+        <v>150</v>
+      </c>
+      <c r="D120" s="41">
+        <v>36174</v>
+      </c>
+      <c r="E120" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F120" s="38">
+        <v>4058000</v>
+      </c>
       <c r="G120" s="38"/>
       <c r="H120" s="46"/>
       <c r="I120" s="65"/>
@@ -9811,12 +11777,26 @@
       <c r="AE120" s="1"/>
       <c r="AF120" s="51"/>
     </row>
-    <row r="121" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B121" s="46"/>
-      <c r="C121" s="55"/>
-      <c r="D121" s="41"/>
-      <c r="E121" s="74"/>
-      <c r="F121" s="38"/>
+    <row r="121" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>87900023</v>
+      </c>
+      <c r="B121" s="46">
+        <f t="shared" si="20"/>
+        <v>110</v>
+      </c>
+      <c r="C121" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="D121" s="41">
+        <v>32142</v>
+      </c>
+      <c r="E121" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F121" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G121" s="38"/>
       <c r="H121" s="46"/>
       <c r="I121" s="65"/>
@@ -9842,12 +11822,26 @@
       <c r="AE121" s="1"/>
       <c r="AF121" s="51"/>
     </row>
-    <row r="122" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B122" s="46"/>
-      <c r="C122" s="55"/>
-      <c r="D122" s="41"/>
-      <c r="E122" s="74"/>
-      <c r="F122" s="38"/>
+    <row r="122" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>87900024</v>
+      </c>
+      <c r="B122" s="46">
+        <f t="shared" si="20"/>
+        <v>111</v>
+      </c>
+      <c r="C122" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="D122" s="41">
+        <v>37312</v>
+      </c>
+      <c r="E122" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F122" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G122" s="38"/>
       <c r="H122" s="46"/>
       <c r="I122" s="65"/>
@@ -9873,12 +11867,26 @@
       <c r="AE122" s="1"/>
       <c r="AF122" s="51"/>
     </row>
-    <row r="123" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B123" s="46"/>
-      <c r="C123" s="55"/>
-      <c r="D123" s="41"/>
-      <c r="E123" s="74"/>
-      <c r="F123" s="38"/>
+    <row r="123" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>87900025</v>
+      </c>
+      <c r="B123" s="46">
+        <f t="shared" si="20"/>
+        <v>112</v>
+      </c>
+      <c r="C123" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="D123" s="41">
+        <v>38730</v>
+      </c>
+      <c r="E123" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F123" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G123" s="38"/>
       <c r="H123" s="46"/>
       <c r="I123" s="65"/>
@@ -9904,12 +11912,26 @@
       <c r="AE123" s="1"/>
       <c r="AF123" s="51"/>
     </row>
-    <row r="124" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B124" s="46"/>
-      <c r="C124" s="55"/>
-      <c r="D124" s="41"/>
-      <c r="E124" s="74"/>
-      <c r="F124" s="38"/>
+    <row r="124" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>87900026</v>
+      </c>
+      <c r="B124" s="46">
+        <f t="shared" si="20"/>
+        <v>113</v>
+      </c>
+      <c r="C124" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="D124" s="41">
+        <v>35359</v>
+      </c>
+      <c r="E124" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F124" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G124" s="38"/>
       <c r="H124" s="46"/>
       <c r="I124" s="65"/>
@@ -9935,12 +11957,26 @@
       <c r="AE124" s="1"/>
       <c r="AF124" s="51"/>
     </row>
-    <row r="125" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B125" s="46"/>
-      <c r="C125" s="55"/>
-      <c r="D125" s="41"/>
-      <c r="E125" s="74"/>
-      <c r="F125" s="38"/>
+    <row r="125" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>87900028</v>
+      </c>
+      <c r="B125" s="46">
+        <f t="shared" si="20"/>
+        <v>114</v>
+      </c>
+      <c r="C125" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="D125" s="41">
+        <v>37389</v>
+      </c>
+      <c r="E125" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F125" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G125" s="38"/>
       <c r="H125" s="46"/>
       <c r="I125" s="65"/>
@@ -9966,12 +12002,26 @@
       <c r="AE125" s="1"/>
       <c r="AF125" s="51"/>
     </row>
-    <row r="126" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B126" s="46"/>
-      <c r="C126" s="55"/>
-      <c r="D126" s="41"/>
-      <c r="E126" s="74"/>
-      <c r="F126" s="38"/>
+    <row r="126" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>87900029</v>
+      </c>
+      <c r="B126" s="46">
+        <f t="shared" si="20"/>
+        <v>115</v>
+      </c>
+      <c r="C126" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="D126" s="41">
+        <v>38008</v>
+      </c>
+      <c r="E126" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F126" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G126" s="38"/>
       <c r="H126" s="46"/>
       <c r="I126" s="65"/>
@@ -9997,12 +12047,26 @@
       <c r="AE126" s="1"/>
       <c r="AF126" s="51"/>
     </row>
-    <row r="127" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B127" s="46"/>
-      <c r="C127" s="55"/>
-      <c r="D127" s="41"/>
-      <c r="E127" s="74"/>
-      <c r="F127" s="38"/>
+    <row r="127" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>87900030</v>
+      </c>
+      <c r="B127" s="46">
+        <f t="shared" si="20"/>
+        <v>116</v>
+      </c>
+      <c r="C127" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="D127" s="41">
+        <v>35752</v>
+      </c>
+      <c r="E127" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F127" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G127" s="38"/>
       <c r="H127" s="46"/>
       <c r="I127" s="65"/>
@@ -10028,12 +12092,26 @@
       <c r="AE127" s="1"/>
       <c r="AF127" s="51"/>
     </row>
-    <row r="128" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B128" s="46"/>
-      <c r="C128" s="55"/>
-      <c r="D128" s="41"/>
-      <c r="E128" s="74"/>
-      <c r="F128" s="38"/>
+    <row r="128" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>87900031</v>
+      </c>
+      <c r="B128" s="46">
+        <f t="shared" si="20"/>
+        <v>117</v>
+      </c>
+      <c r="C128" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="D128" s="41">
+        <v>36282</v>
+      </c>
+      <c r="E128" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F128" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G128" s="38"/>
       <c r="H128" s="46"/>
       <c r="I128" s="65"/>
@@ -10059,11 +12137,26 @@
       <c r="AE128" s="1"/>
       <c r="AF128" s="51"/>
     </row>
-    <row r="129" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B129" s="46"/>
-      <c r="D129" s="37"/>
-      <c r="E129" s="10"/>
-      <c r="F129" s="78"/>
+    <row r="129" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>87900032</v>
+      </c>
+      <c r="B129" s="46">
+        <f t="shared" si="20"/>
+        <v>118</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D129" s="37">
+        <v>37231</v>
+      </c>
+      <c r="E129" s="10">
+        <v>45790</v>
+      </c>
+      <c r="F129" s="78">
+        <v>3958000</v>
+      </c>
       <c r="G129" s="78"/>
       <c r="H129" s="46"/>
       <c r="I129" s="65"/>
@@ -10089,12 +12182,26 @@
       <c r="AE129" s="1"/>
       <c r="AF129" s="51"/>
     </row>
-    <row r="130" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B130" s="46"/>
-      <c r="C130" s="79"/>
-      <c r="D130" s="41"/>
-      <c r="E130" s="74"/>
-      <c r="F130" s="38"/>
+    <row r="130" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>87900033</v>
+      </c>
+      <c r="B130" s="46">
+        <f t="shared" si="20"/>
+        <v>119</v>
+      </c>
+      <c r="C130" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="D130" s="41">
+        <v>38555</v>
+      </c>
+      <c r="E130" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F130" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G130" s="38"/>
       <c r="H130" s="46"/>
       <c r="I130" s="65"/>
@@ -10120,12 +12227,26 @@
       <c r="AE130" s="1"/>
       <c r="AF130" s="51"/>
     </row>
-    <row r="131" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B131" s="46"/>
-      <c r="C131" s="79"/>
-      <c r="D131" s="41"/>
-      <c r="E131" s="74"/>
-      <c r="F131" s="38"/>
+    <row r="131" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>87900034</v>
+      </c>
+      <c r="B131" s="46">
+        <f t="shared" si="20"/>
+        <v>120</v>
+      </c>
+      <c r="C131" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="D131" s="41">
+        <v>38345</v>
+      </c>
+      <c r="E131" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F131" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G131" s="38"/>
       <c r="H131" s="46"/>
       <c r="I131" s="80"/>
@@ -10151,12 +12272,26 @@
       <c r="AE131" s="1"/>
       <c r="AF131" s="51"/>
     </row>
-    <row r="132" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B132" s="46"/>
-      <c r="C132" s="79"/>
-      <c r="D132" s="41"/>
-      <c r="E132" s="74"/>
-      <c r="F132" s="38"/>
+    <row r="132" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>87900035</v>
+      </c>
+      <c r="B132" s="46">
+        <f t="shared" si="20"/>
+        <v>121</v>
+      </c>
+      <c r="C132" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="D132" s="41">
+        <v>39023</v>
+      </c>
+      <c r="E132" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F132" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G132" s="38"/>
       <c r="H132" s="46"/>
       <c r="I132" s="80"/>
@@ -10182,12 +12317,26 @@
       <c r="AE132" s="1"/>
       <c r="AF132" s="51"/>
     </row>
-    <row r="133" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B133" s="46"/>
-      <c r="C133" s="79"/>
-      <c r="D133" s="41"/>
-      <c r="E133" s="74"/>
-      <c r="F133" s="38"/>
+    <row r="133" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>87900036</v>
+      </c>
+      <c r="B133" s="46">
+        <f t="shared" si="20"/>
+        <v>122</v>
+      </c>
+      <c r="C133" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="D133" s="41">
+        <v>37428</v>
+      </c>
+      <c r="E133" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F133" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G133" s="38"/>
       <c r="H133" s="46"/>
       <c r="I133" s="80"/>
@@ -10213,12 +12362,26 @@
       <c r="AE133" s="1"/>
       <c r="AF133" s="51"/>
     </row>
-    <row r="134" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B134" s="46"/>
-      <c r="C134" s="79"/>
-      <c r="D134" s="41"/>
-      <c r="E134" s="74"/>
-      <c r="F134" s="38"/>
+    <row r="134" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>87900037</v>
+      </c>
+      <c r="B134" s="46">
+        <f t="shared" si="20"/>
+        <v>123</v>
+      </c>
+      <c r="C134" s="79" t="s">
+        <v>164</v>
+      </c>
+      <c r="D134" s="41">
+        <v>35521</v>
+      </c>
+      <c r="E134" s="74">
+        <v>45790</v>
+      </c>
+      <c r="F134" s="38">
+        <v>4158000</v>
+      </c>
       <c r="G134" s="38"/>
       <c r="H134" s="46"/>
       <c r="I134" s="80"/>
@@ -10244,12 +12407,26 @@
       <c r="AE134" s="1"/>
       <c r="AF134" s="51"/>
     </row>
-    <row r="135" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B135" s="46"/>
-      <c r="C135" s="79"/>
-      <c r="D135" s="41"/>
-      <c r="E135" s="74"/>
-      <c r="F135" s="38"/>
+    <row r="135" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>87900038</v>
+      </c>
+      <c r="B135" s="46">
+        <f t="shared" si="20"/>
+        <v>124</v>
+      </c>
+      <c r="C135" s="79" t="s">
+        <v>165</v>
+      </c>
+      <c r="D135" s="41">
+        <v>35855</v>
+      </c>
+      <c r="E135" s="74">
+        <v>45798</v>
+      </c>
+      <c r="F135" s="38">
+        <v>4058000</v>
+      </c>
       <c r="G135" s="38"/>
       <c r="H135" s="46"/>
       <c r="I135" s="80"/>
@@ -10275,12 +12452,26 @@
       <c r="AE135" s="1"/>
       <c r="AF135" s="51"/>
     </row>
-    <row r="136" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B136" s="46"/>
-      <c r="C136" s="79"/>
-      <c r="D136" s="41"/>
-      <c r="E136" s="74"/>
-      <c r="F136" s="38"/>
+    <row r="136" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>87900039</v>
+      </c>
+      <c r="B136" s="46">
+        <f t="shared" si="20"/>
+        <v>125</v>
+      </c>
+      <c r="C136" s="79" t="s">
+        <v>166</v>
+      </c>
+      <c r="D136" s="41">
+        <v>37096</v>
+      </c>
+      <c r="E136" s="74">
+        <v>45798</v>
+      </c>
+      <c r="F136" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G136" s="38"/>
       <c r="H136" s="46"/>
       <c r="I136" s="80"/>
@@ -10306,12 +12497,26 @@
       <c r="AE136" s="1"/>
       <c r="AF136" s="51"/>
     </row>
-    <row r="137" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B137" s="46"/>
-      <c r="C137" s="79"/>
-      <c r="D137" s="41"/>
-      <c r="E137" s="74"/>
-      <c r="F137" s="38"/>
+    <row r="137" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>87900041</v>
+      </c>
+      <c r="B137" s="46">
+        <f t="shared" si="20"/>
+        <v>126</v>
+      </c>
+      <c r="C137" s="79" t="s">
+        <v>167</v>
+      </c>
+      <c r="D137" s="41">
+        <v>38272</v>
+      </c>
+      <c r="E137" s="74">
+        <v>45798</v>
+      </c>
+      <c r="F137" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G137" s="38"/>
       <c r="H137" s="46"/>
       <c r="I137" s="80"/>
@@ -10337,12 +12542,26 @@
       <c r="AE137" s="1"/>
       <c r="AF137" s="51"/>
     </row>
-    <row r="138" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B138" s="46"/>
-      <c r="C138" s="79"/>
-      <c r="D138" s="41"/>
-      <c r="E138" s="74"/>
-      <c r="F138" s="38"/>
+    <row r="138" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>87900042</v>
+      </c>
+      <c r="B138" s="46">
+        <f t="shared" si="20"/>
+        <v>127</v>
+      </c>
+      <c r="C138" s="79" t="s">
+        <v>168</v>
+      </c>
+      <c r="D138" s="41">
+        <v>38925</v>
+      </c>
+      <c r="E138" s="74">
+        <v>45798</v>
+      </c>
+      <c r="F138" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G138" s="38"/>
       <c r="H138" s="46"/>
       <c r="I138" s="80"/>
@@ -10368,12 +12587,26 @@
       <c r="AE138" s="1"/>
       <c r="AF138" s="51"/>
     </row>
-    <row r="139" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B139" s="46"/>
-      <c r="C139" s="79"/>
-      <c r="D139" s="41"/>
-      <c r="E139" s="74"/>
-      <c r="F139" s="38"/>
+    <row r="139" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>87900043</v>
+      </c>
+      <c r="B139" s="46">
+        <f t="shared" si="20"/>
+        <v>128</v>
+      </c>
+      <c r="C139" s="79" t="s">
+        <v>169</v>
+      </c>
+      <c r="D139" s="41">
+        <v>38831</v>
+      </c>
+      <c r="E139" s="74">
+        <v>45798</v>
+      </c>
+      <c r="F139" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G139" s="38"/>
       <c r="H139" s="46"/>
       <c r="I139" s="80"/>
@@ -10399,12 +12632,26 @@
       <c r="AE139" s="1"/>
       <c r="AF139" s="51"/>
     </row>
-    <row r="140" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B140" s="46"/>
-      <c r="C140" s="79"/>
-      <c r="D140" s="41"/>
-      <c r="E140" s="74"/>
-      <c r="F140" s="38"/>
+    <row r="140" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>87900044</v>
+      </c>
+      <c r="B140" s="46">
+        <f t="shared" si="20"/>
+        <v>129</v>
+      </c>
+      <c r="C140" s="79" t="s">
+        <v>170</v>
+      </c>
+      <c r="D140" s="41">
+        <v>37554</v>
+      </c>
+      <c r="E140" s="74">
+        <v>45798</v>
+      </c>
+      <c r="F140" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G140" s="38"/>
       <c r="H140" s="46"/>
       <c r="I140" s="80"/>
@@ -10430,12 +12677,26 @@
       <c r="AE140" s="1"/>
       <c r="AF140" s="51"/>
     </row>
-    <row r="141" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B141" s="46"/>
-      <c r="C141" s="79"/>
-      <c r="D141" s="41"/>
-      <c r="E141" s="74"/>
-      <c r="F141" s="38"/>
+    <row r="141" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>87900045</v>
+      </c>
+      <c r="B141" s="46">
+        <f t="shared" ref="B141:B187" si="21">B140+1</f>
+        <v>130</v>
+      </c>
+      <c r="C141" s="79" t="s">
+        <v>171</v>
+      </c>
+      <c r="D141" s="41">
+        <v>38092</v>
+      </c>
+      <c r="E141" s="74">
+        <v>45798</v>
+      </c>
+      <c r="F141" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G141" s="38"/>
       <c r="H141" s="46"/>
       <c r="I141" s="80"/>
@@ -10461,12 +12722,26 @@
       <c r="AE141" s="1"/>
       <c r="AF141" s="51"/>
     </row>
-    <row r="142" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B142" s="46"/>
-      <c r="C142" s="79"/>
-      <c r="D142" s="41"/>
-      <c r="E142" s="74"/>
-      <c r="F142" s="38"/>
+    <row r="142" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>87900046</v>
+      </c>
+      <c r="B142" s="46">
+        <f t="shared" si="21"/>
+        <v>131</v>
+      </c>
+      <c r="C142" s="79" t="s">
+        <v>172</v>
+      </c>
+      <c r="D142" s="41">
+        <v>37033</v>
+      </c>
+      <c r="E142" s="74">
+        <v>45798</v>
+      </c>
+      <c r="F142" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G142" s="38"/>
       <c r="H142" s="46"/>
       <c r="I142" s="80"/>
@@ -10492,12 +12767,26 @@
       <c r="AE142" s="1"/>
       <c r="AF142" s="51"/>
     </row>
-    <row r="143" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B143" s="46"/>
-      <c r="C143" s="79"/>
-      <c r="D143" s="41"/>
-      <c r="E143" s="74"/>
-      <c r="F143" s="38"/>
+    <row r="143" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>87900047</v>
+      </c>
+      <c r="B143" s="46">
+        <f t="shared" si="21"/>
+        <v>132</v>
+      </c>
+      <c r="C143" s="79" t="s">
+        <v>173</v>
+      </c>
+      <c r="D143" s="41">
+        <v>38429</v>
+      </c>
+      <c r="E143" s="74">
+        <v>45798</v>
+      </c>
+      <c r="F143" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G143" s="38"/>
       <c r="H143" s="46"/>
       <c r="I143" s="80"/>
@@ -10523,12 +12812,26 @@
       <c r="AE143" s="1"/>
       <c r="AF143" s="51"/>
     </row>
-    <row r="144" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B144" s="46"/>
-      <c r="C144" s="79"/>
-      <c r="D144" s="41"/>
-      <c r="E144" s="74"/>
-      <c r="F144" s="38"/>
+    <row r="144" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>87900048</v>
+      </c>
+      <c r="B144" s="46">
+        <f t="shared" si="21"/>
+        <v>133</v>
+      </c>
+      <c r="C144" s="79" t="s">
+        <v>174</v>
+      </c>
+      <c r="D144" s="41">
+        <v>37435</v>
+      </c>
+      <c r="E144" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F144" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G144" s="38"/>
       <c r="H144" s="46"/>
       <c r="I144" s="80"/>
@@ -10554,12 +12857,26 @@
       <c r="AE144" s="1"/>
       <c r="AF144" s="51"/>
     </row>
-    <row r="145" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B145" s="46"/>
-      <c r="C145" s="79"/>
-      <c r="D145" s="41"/>
-      <c r="E145" s="74"/>
-      <c r="F145" s="38"/>
+    <row r="145" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>87900049</v>
+      </c>
+      <c r="B145" s="46">
+        <f t="shared" si="21"/>
+        <v>134</v>
+      </c>
+      <c r="C145" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="D145" s="41">
+        <v>36494</v>
+      </c>
+      <c r="E145" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F145" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G145" s="38"/>
       <c r="H145" s="46"/>
       <c r="I145" s="80"/>
@@ -10585,12 +12902,26 @@
       <c r="AE145" s="1"/>
       <c r="AF145" s="51"/>
     </row>
-    <row r="146" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B146" s="46"/>
-      <c r="C146" s="79"/>
-      <c r="D146" s="41"/>
-      <c r="E146" s="74"/>
-      <c r="F146" s="38"/>
+    <row r="146" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>87900050</v>
+      </c>
+      <c r="B146" s="46">
+        <f t="shared" si="21"/>
+        <v>135</v>
+      </c>
+      <c r="C146" s="79" t="s">
+        <v>176</v>
+      </c>
+      <c r="D146" s="41">
+        <v>36608</v>
+      </c>
+      <c r="E146" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F146" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G146" s="38"/>
       <c r="H146" s="46"/>
       <c r="I146" s="80"/>
@@ -10616,12 +12947,26 @@
       <c r="AE146" s="1"/>
       <c r="AF146" s="51"/>
     </row>
-    <row r="147" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B147" s="46"/>
-      <c r="C147" s="79"/>
-      <c r="D147" s="41"/>
-      <c r="E147" s="74"/>
-      <c r="F147" s="38"/>
+    <row r="147" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>87900051</v>
+      </c>
+      <c r="B147" s="46">
+        <f t="shared" si="21"/>
+        <v>136</v>
+      </c>
+      <c r="C147" s="79" t="s">
+        <v>176</v>
+      </c>
+      <c r="D147" s="41">
+        <v>36254</v>
+      </c>
+      <c r="E147" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F147" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G147" s="38"/>
       <c r="H147" s="46"/>
       <c r="I147" s="80"/>
@@ -10647,12 +12992,26 @@
       <c r="AE147" s="1"/>
       <c r="AF147" s="51"/>
     </row>
-    <row r="148" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B148" s="46"/>
-      <c r="C148" s="79"/>
-      <c r="D148" s="41"/>
-      <c r="E148" s="74"/>
-      <c r="F148" s="38"/>
+    <row r="148" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>87900052</v>
+      </c>
+      <c r="B148" s="46">
+        <f t="shared" si="21"/>
+        <v>137</v>
+      </c>
+      <c r="C148" s="79" t="s">
+        <v>177</v>
+      </c>
+      <c r="D148" s="41">
+        <v>36233</v>
+      </c>
+      <c r="E148" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F148" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G148" s="38"/>
       <c r="H148" s="46"/>
       <c r="I148" s="80"/>
@@ -10678,12 +13037,26 @@
       <c r="AE148" s="1"/>
       <c r="AF148" s="51"/>
     </row>
-    <row r="149" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B149" s="46"/>
-      <c r="C149" s="79"/>
-      <c r="D149" s="41"/>
-      <c r="E149" s="74"/>
-      <c r="F149" s="38"/>
+    <row r="149" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>87900053</v>
+      </c>
+      <c r="B149" s="46">
+        <f t="shared" si="21"/>
+        <v>138</v>
+      </c>
+      <c r="C149" s="79" t="s">
+        <v>178</v>
+      </c>
+      <c r="D149" s="41">
+        <v>36083</v>
+      </c>
+      <c r="E149" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F149" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G149" s="38"/>
       <c r="H149" s="46"/>
       <c r="I149" s="80"/>
@@ -10709,12 +13082,26 @@
       <c r="AE149" s="1"/>
       <c r="AF149" s="51"/>
     </row>
-    <row r="150" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B150" s="46"/>
-      <c r="C150" s="79"/>
-      <c r="D150" s="41"/>
-      <c r="E150" s="74"/>
-      <c r="F150" s="38"/>
+    <row r="150" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>87900054</v>
+      </c>
+      <c r="B150" s="46">
+        <f t="shared" si="21"/>
+        <v>139</v>
+      </c>
+      <c r="C150" s="79" t="s">
+        <v>179</v>
+      </c>
+      <c r="D150" s="41">
+        <v>37134</v>
+      </c>
+      <c r="E150" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F150" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G150" s="38"/>
       <c r="H150" s="46"/>
       <c r="I150" s="80"/>
@@ -10740,12 +13127,26 @@
       <c r="AE150" s="1"/>
       <c r="AF150" s="51"/>
     </row>
-    <row r="151" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B151" s="46"/>
-      <c r="C151" s="79"/>
-      <c r="D151" s="41"/>
-      <c r="E151" s="74"/>
-      <c r="F151" s="38"/>
+    <row r="151" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>87900055</v>
+      </c>
+      <c r="B151" s="46">
+        <f t="shared" si="21"/>
+        <v>140</v>
+      </c>
+      <c r="C151" s="79" t="s">
+        <v>180</v>
+      </c>
+      <c r="D151" s="41">
+        <v>36633</v>
+      </c>
+      <c r="E151" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F151" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G151" s="38"/>
       <c r="H151" s="46"/>
       <c r="I151" s="80"/>
@@ -10771,12 +13172,26 @@
       <c r="AE151" s="1"/>
       <c r="AF151" s="51"/>
     </row>
-    <row r="152" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B152" s="46"/>
-      <c r="C152" s="79"/>
-      <c r="D152" s="41"/>
-      <c r="E152" s="74"/>
-      <c r="F152" s="38"/>
+    <row r="152" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>87900056</v>
+      </c>
+      <c r="B152" s="46">
+        <f t="shared" si="21"/>
+        <v>141</v>
+      </c>
+      <c r="C152" s="79" t="s">
+        <v>181</v>
+      </c>
+      <c r="D152" s="41">
+        <v>37037</v>
+      </c>
+      <c r="E152" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F152" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G152" s="38"/>
       <c r="H152" s="46"/>
       <c r="I152" s="80"/>
@@ -10802,12 +13217,26 @@
       <c r="AE152" s="1"/>
       <c r="AF152" s="51"/>
     </row>
-    <row r="153" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B153" s="46"/>
-      <c r="C153" s="79"/>
-      <c r="D153" s="41"/>
-      <c r="E153" s="74"/>
-      <c r="F153" s="38"/>
+    <row r="153" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>87900057</v>
+      </c>
+      <c r="B153" s="46">
+        <f t="shared" si="21"/>
+        <v>142</v>
+      </c>
+      <c r="C153" s="79" t="s">
+        <v>182</v>
+      </c>
+      <c r="D153" s="41">
+        <v>37030</v>
+      </c>
+      <c r="E153" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F153" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G153" s="38"/>
       <c r="H153" s="46"/>
       <c r="I153" s="80"/>
@@ -10833,12 +13262,26 @@
       <c r="AE153" s="1"/>
       <c r="AF153" s="51"/>
     </row>
-    <row r="154" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B154" s="46"/>
-      <c r="C154" s="79"/>
-      <c r="D154" s="41"/>
-      <c r="E154" s="74"/>
-      <c r="F154" s="38"/>
+    <row r="154" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>87900058</v>
+      </c>
+      <c r="B154" s="46">
+        <f t="shared" si="21"/>
+        <v>143</v>
+      </c>
+      <c r="C154" s="79" t="s">
+        <v>183</v>
+      </c>
+      <c r="D154" s="41">
+        <v>36583</v>
+      </c>
+      <c r="E154" s="74">
+        <v>45805</v>
+      </c>
+      <c r="F154" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G154" s="38"/>
       <c r="H154" s="46"/>
       <c r="I154" s="80"/>
@@ -10864,12 +13307,26 @@
       <c r="AE154" s="1"/>
       <c r="AF154" s="51"/>
     </row>
-    <row r="155" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B155" s="46"/>
-      <c r="C155" s="79"/>
-      <c r="D155" s="41"/>
-      <c r="E155" s="74"/>
-      <c r="F155" s="38"/>
+    <row r="155" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>87900060</v>
+      </c>
+      <c r="B155" s="46">
+        <f t="shared" si="21"/>
+        <v>144</v>
+      </c>
+      <c r="C155" s="79" t="s">
+        <v>184</v>
+      </c>
+      <c r="D155" s="41">
+        <v>36823</v>
+      </c>
+      <c r="E155" s="74">
+        <v>45813</v>
+      </c>
+      <c r="F155" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G155" s="38"/>
       <c r="H155" s="46"/>
       <c r="I155" s="80"/>
@@ -10895,12 +13352,26 @@
       <c r="AE155" s="1"/>
       <c r="AF155" s="51"/>
     </row>
-    <row r="156" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B156" s="46"/>
-      <c r="C156" s="79"/>
-      <c r="D156" s="41"/>
-      <c r="E156" s="74"/>
-      <c r="F156" s="38"/>
+    <row r="156" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>87900061</v>
+      </c>
+      <c r="B156" s="46">
+        <f t="shared" si="21"/>
+        <v>145</v>
+      </c>
+      <c r="C156" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="D156" s="41">
+        <v>35971</v>
+      </c>
+      <c r="E156" s="74">
+        <v>45813</v>
+      </c>
+      <c r="F156" s="38">
+        <v>4158000</v>
+      </c>
       <c r="G156" s="38"/>
       <c r="H156" s="46"/>
       <c r="I156" s="80"/>
@@ -10926,12 +13397,26 @@
       <c r="AE156" s="1"/>
       <c r="AF156" s="51"/>
     </row>
-    <row r="157" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B157" s="46"/>
-      <c r="C157" s="79"/>
-      <c r="D157" s="41"/>
-      <c r="E157" s="74"/>
-      <c r="F157" s="38"/>
+    <row r="157" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>87900062</v>
+      </c>
+      <c r="B157" s="46">
+        <f t="shared" si="21"/>
+        <v>146</v>
+      </c>
+      <c r="C157" s="79" t="s">
+        <v>185</v>
+      </c>
+      <c r="D157" s="41">
+        <v>37103</v>
+      </c>
+      <c r="E157" s="74">
+        <v>45813</v>
+      </c>
+      <c r="F157" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G157" s="38"/>
       <c r="H157" s="46"/>
       <c r="I157" s="80"/>
@@ -10957,12 +13442,26 @@
       <c r="AE157" s="1"/>
       <c r="AF157" s="51"/>
     </row>
-    <row r="158" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B158" s="46"/>
-      <c r="C158" s="79"/>
-      <c r="D158" s="41"/>
-      <c r="E158" s="74"/>
-      <c r="F158" s="38"/>
+    <row r="158" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>87900063</v>
+      </c>
+      <c r="B158" s="46">
+        <f t="shared" si="21"/>
+        <v>147</v>
+      </c>
+      <c r="C158" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D158" s="41">
+        <v>35987</v>
+      </c>
+      <c r="E158" s="74">
+        <v>45813</v>
+      </c>
+      <c r="F158" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G158" s="38"/>
       <c r="H158" s="46"/>
       <c r="I158" s="80"/>
@@ -10988,12 +13487,26 @@
       <c r="AE158" s="1"/>
       <c r="AF158" s="51"/>
     </row>
-    <row r="159" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B159" s="46"/>
-      <c r="C159" s="79"/>
-      <c r="D159" s="41"/>
-      <c r="E159" s="74"/>
-      <c r="F159" s="38"/>
+    <row r="159" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>87900064</v>
+      </c>
+      <c r="B159" s="46">
+        <f t="shared" si="21"/>
+        <v>148</v>
+      </c>
+      <c r="C159" s="79" t="s">
+        <v>187</v>
+      </c>
+      <c r="D159" s="41">
+        <v>36144</v>
+      </c>
+      <c r="E159" s="74">
+        <v>45813</v>
+      </c>
+      <c r="F159" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G159" s="38"/>
       <c r="H159" s="46"/>
       <c r="I159" s="80"/>
@@ -11019,12 +13532,26 @@
       <c r="AE159" s="1"/>
       <c r="AF159" s="51"/>
     </row>
-    <row r="160" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B160" s="46"/>
-      <c r="C160" s="79"/>
-      <c r="D160" s="41"/>
-      <c r="E160" s="74"/>
-      <c r="F160" s="38"/>
+    <row r="160" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>87900065</v>
+      </c>
+      <c r="B160" s="46">
+        <f t="shared" si="21"/>
+        <v>149</v>
+      </c>
+      <c r="C160" s="79" t="s">
+        <v>188</v>
+      </c>
+      <c r="D160" s="41">
+        <v>37023</v>
+      </c>
+      <c r="E160" s="74">
+        <v>45821</v>
+      </c>
+      <c r="F160" s="38">
+        <v>4058000</v>
+      </c>
       <c r="G160" s="38"/>
       <c r="H160" s="46"/>
       <c r="I160" s="80"/>
@@ -11050,12 +13577,26 @@
       <c r="AE160" s="1"/>
       <c r="AF160" s="51"/>
     </row>
-    <row r="161" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B161" s="46"/>
-      <c r="C161" s="81"/>
-      <c r="D161" s="54"/>
-      <c r="E161" s="37"/>
-      <c r="F161" s="82"/>
+    <row r="161" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>87900067</v>
+      </c>
+      <c r="B161" s="46">
+        <f t="shared" si="21"/>
+        <v>150</v>
+      </c>
+      <c r="C161" s="81" t="s">
+        <v>189</v>
+      </c>
+      <c r="D161" s="54">
+        <v>37800</v>
+      </c>
+      <c r="E161" s="37">
+        <v>45821</v>
+      </c>
+      <c r="F161" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G161" s="82"/>
       <c r="H161" s="46"/>
       <c r="I161" s="80"/>
@@ -11081,12 +13622,26 @@
       <c r="AE161" s="1"/>
       <c r="AF161" s="51"/>
     </row>
-    <row r="162" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B162" s="46"/>
-      <c r="C162" s="81"/>
-      <c r="D162" s="54"/>
-      <c r="E162" s="37"/>
-      <c r="F162" s="82"/>
+    <row r="162" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>87900070</v>
+      </c>
+      <c r="B162" s="46">
+        <f t="shared" si="21"/>
+        <v>151</v>
+      </c>
+      <c r="C162" s="81" t="s">
+        <v>190</v>
+      </c>
+      <c r="D162" s="54">
+        <v>37508</v>
+      </c>
+      <c r="E162" s="37">
+        <v>45821</v>
+      </c>
+      <c r="F162" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G162" s="82"/>
       <c r="H162" s="46"/>
       <c r="I162" s="80"/>
@@ -11112,12 +13667,26 @@
       <c r="AE162" s="1"/>
       <c r="AF162" s="51"/>
     </row>
-    <row r="163" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B163" s="46"/>
-      <c r="C163" s="81"/>
-      <c r="D163" s="54"/>
-      <c r="E163" s="37"/>
-      <c r="F163" s="82"/>
+    <row r="163" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>87900075</v>
+      </c>
+      <c r="B163" s="46">
+        <f t="shared" si="21"/>
+        <v>152</v>
+      </c>
+      <c r="C163" s="81" t="s">
+        <v>191</v>
+      </c>
+      <c r="D163" s="54">
+        <v>38780</v>
+      </c>
+      <c r="E163" s="37">
+        <v>45821</v>
+      </c>
+      <c r="F163" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G163" s="82"/>
       <c r="H163" s="46"/>
       <c r="I163" s="80"/>
@@ -11143,12 +13712,26 @@
       <c r="AE163" s="1"/>
       <c r="AF163" s="51"/>
     </row>
-    <row r="164" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B164" s="46"/>
-      <c r="C164" s="83"/>
-      <c r="D164" s="84"/>
-      <c r="E164" s="37"/>
-      <c r="F164" s="82"/>
+    <row r="164" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>87900077</v>
+      </c>
+      <c r="B164" s="46">
+        <f t="shared" si="21"/>
+        <v>153</v>
+      </c>
+      <c r="C164" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="D164" s="84">
+        <v>36823</v>
+      </c>
+      <c r="E164" s="37">
+        <v>45821</v>
+      </c>
+      <c r="F164" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G164" s="82"/>
       <c r="H164" s="46"/>
       <c r="I164" s="80"/>
@@ -11174,12 +13757,26 @@
       <c r="AE164" s="1"/>
       <c r="AF164" s="51"/>
     </row>
-    <row r="165" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B165" s="46"/>
-      <c r="C165" s="81"/>
-      <c r="D165" s="41"/>
-      <c r="E165" s="74"/>
-      <c r="F165" s="82"/>
+    <row r="165" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>87900091</v>
+      </c>
+      <c r="B165" s="46">
+        <f t="shared" si="21"/>
+        <v>154</v>
+      </c>
+      <c r="C165" s="81" t="s">
+        <v>193</v>
+      </c>
+      <c r="D165" s="41">
+        <v>37529</v>
+      </c>
+      <c r="E165" s="74">
+        <v>45821</v>
+      </c>
+      <c r="F165" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G165" s="82"/>
       <c r="H165" s="46"/>
       <c r="I165" s="80"/>
@@ -11205,12 +13802,26 @@
       <c r="AE165" s="1"/>
       <c r="AF165" s="51"/>
     </row>
-    <row r="166" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B166" s="46"/>
-      <c r="C166" s="81"/>
-      <c r="D166" s="54"/>
-      <c r="E166" s="37"/>
-      <c r="F166" s="82"/>
+    <row r="166" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>87900092</v>
+      </c>
+      <c r="B166" s="46">
+        <f t="shared" si="21"/>
+        <v>155</v>
+      </c>
+      <c r="C166" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="D166" s="54">
+        <v>39232</v>
+      </c>
+      <c r="E166" s="37">
+        <v>45836</v>
+      </c>
+      <c r="F166" s="82">
+        <v>4058000</v>
+      </c>
       <c r="G166" s="82"/>
       <c r="H166" s="46"/>
       <c r="I166" s="80"/>
@@ -11236,12 +13847,26 @@
       <c r="AE166" s="1"/>
       <c r="AF166" s="51"/>
     </row>
-    <row r="167" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B167" s="46"/>
-      <c r="C167" s="81"/>
-      <c r="D167" s="54"/>
-      <c r="E167" s="37"/>
-      <c r="F167" s="82"/>
+    <row r="167" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>87900093</v>
+      </c>
+      <c r="B167" s="46">
+        <f t="shared" si="21"/>
+        <v>156</v>
+      </c>
+      <c r="C167" s="81" t="s">
+        <v>195</v>
+      </c>
+      <c r="D167" s="54">
+        <v>39103</v>
+      </c>
+      <c r="E167" s="37">
+        <v>45836</v>
+      </c>
+      <c r="F167" s="82">
+        <v>4058000</v>
+      </c>
       <c r="G167" s="82"/>
       <c r="H167" s="46"/>
       <c r="I167" s="80"/>
@@ -11267,12 +13892,26 @@
       <c r="AE167" s="1"/>
       <c r="AF167" s="51"/>
     </row>
-    <row r="168" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B168" s="46"/>
-      <c r="C168" s="81"/>
-      <c r="D168" s="54"/>
-      <c r="E168" s="37"/>
-      <c r="F168" s="82"/>
+    <row r="168" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>87900066</v>
+      </c>
+      <c r="B168" s="46">
+        <f t="shared" si="21"/>
+        <v>157</v>
+      </c>
+      <c r="C168" s="81" t="s">
+        <v>196</v>
+      </c>
+      <c r="D168" s="54">
+        <v>38391</v>
+      </c>
+      <c r="E168" s="37">
+        <v>45843</v>
+      </c>
+      <c r="F168" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G168" s="82"/>
       <c r="H168" s="46"/>
       <c r="I168" s="80"/>
@@ -11298,12 +13937,26 @@
       <c r="AE168" s="1"/>
       <c r="AF168" s="51"/>
     </row>
-    <row r="169" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B169" s="46"/>
-      <c r="C169" s="81"/>
-      <c r="D169" s="54"/>
-      <c r="E169" s="37"/>
-      <c r="F169" s="82"/>
+    <row r="169" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A169" s="1">
+        <v>87900068</v>
+      </c>
+      <c r="B169" s="46">
+        <f t="shared" si="21"/>
+        <v>158</v>
+      </c>
+      <c r="C169" s="81" t="s">
+        <v>197</v>
+      </c>
+      <c r="D169" s="54">
+        <v>37438</v>
+      </c>
+      <c r="E169" s="37">
+        <v>45843</v>
+      </c>
+      <c r="F169" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G169" s="82"/>
       <c r="H169" s="46"/>
       <c r="I169" s="85"/>
@@ -11329,12 +13982,26 @@
       <c r="AE169" s="1"/>
       <c r="AF169" s="51"/>
     </row>
-    <row r="170" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B170" s="46"/>
-      <c r="C170" s="81"/>
-      <c r="D170" s="54"/>
-      <c r="E170" s="37"/>
-      <c r="F170" s="82"/>
+    <row r="170" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>87900071</v>
+      </c>
+      <c r="B170" s="46">
+        <f t="shared" si="21"/>
+        <v>159</v>
+      </c>
+      <c r="C170" s="81" t="s">
+        <v>198</v>
+      </c>
+      <c r="D170" s="54">
+        <v>34710</v>
+      </c>
+      <c r="E170" s="37">
+        <v>45843</v>
+      </c>
+      <c r="F170" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G170" s="82"/>
       <c r="H170" s="46"/>
       <c r="I170" s="85"/>
@@ -11360,12 +14027,26 @@
       <c r="AE170" s="1"/>
       <c r="AF170" s="51"/>
     </row>
-    <row r="171" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B171" s="46"/>
-      <c r="C171" s="81"/>
-      <c r="D171" s="54"/>
-      <c r="E171" s="37"/>
-      <c r="F171" s="82"/>
+    <row r="171" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>87900074</v>
+      </c>
+      <c r="B171" s="46">
+        <f t="shared" si="21"/>
+        <v>160</v>
+      </c>
+      <c r="C171" s="81" t="s">
+        <v>199</v>
+      </c>
+      <c r="D171" s="54">
+        <v>38201</v>
+      </c>
+      <c r="E171" s="37">
+        <v>45843</v>
+      </c>
+      <c r="F171" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G171" s="82"/>
       <c r="H171" s="46"/>
       <c r="I171" s="85"/>
@@ -11391,12 +14072,26 @@
       <c r="AE171" s="1"/>
       <c r="AF171" s="51"/>
     </row>
-    <row r="172" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B172" s="46"/>
-      <c r="C172" s="81"/>
-      <c r="D172" s="54"/>
-      <c r="E172" s="37"/>
-      <c r="F172" s="82"/>
+    <row r="172" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>87900081</v>
+      </c>
+      <c r="B172" s="46">
+        <f t="shared" si="21"/>
+        <v>161</v>
+      </c>
+      <c r="C172" s="81" t="s">
+        <v>200</v>
+      </c>
+      <c r="D172" s="54">
+        <v>35688</v>
+      </c>
+      <c r="E172" s="37">
+        <v>45843</v>
+      </c>
+      <c r="F172" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G172" s="82"/>
       <c r="H172" s="46"/>
       <c r="I172" s="85"/>
@@ -11422,12 +14117,26 @@
       <c r="AE172" s="1"/>
       <c r="AF172" s="51"/>
     </row>
-    <row r="173" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B173" s="46"/>
-      <c r="C173" s="81"/>
-      <c r="D173" s="54"/>
-      <c r="E173" s="37"/>
-      <c r="F173" s="82"/>
+    <row r="173" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>87900082</v>
+      </c>
+      <c r="B173" s="46">
+        <f t="shared" si="21"/>
+        <v>162</v>
+      </c>
+      <c r="C173" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="D173" s="54">
+        <v>37413</v>
+      </c>
+      <c r="E173" s="37">
+        <v>45843</v>
+      </c>
+      <c r="F173" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G173" s="82"/>
       <c r="H173" s="46"/>
       <c r="I173" s="85"/>
@@ -11453,12 +14162,26 @@
       <c r="AE173" s="1"/>
       <c r="AF173" s="51"/>
     </row>
-    <row r="174" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B174" s="46"/>
-      <c r="C174" s="81"/>
-      <c r="D174" s="54"/>
-      <c r="E174" s="37"/>
-      <c r="F174" s="82"/>
+    <row r="174" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>87900083</v>
+      </c>
+      <c r="B174" s="46">
+        <f t="shared" si="21"/>
+        <v>163</v>
+      </c>
+      <c r="C174" s="81" t="s">
+        <v>202</v>
+      </c>
+      <c r="D174" s="54">
+        <v>35825</v>
+      </c>
+      <c r="E174" s="37">
+        <v>45843</v>
+      </c>
+      <c r="F174" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G174" s="82"/>
       <c r="H174" s="46"/>
       <c r="I174" s="85"/>
@@ -11484,12 +14207,26 @@
       <c r="AE174" s="1"/>
       <c r="AF174" s="51"/>
     </row>
-    <row r="175" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B175" s="46"/>
-      <c r="C175" s="83"/>
-      <c r="D175" s="84"/>
-      <c r="E175" s="37"/>
-      <c r="F175" s="82"/>
+    <row r="175" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>87900084</v>
+      </c>
+      <c r="B175" s="46">
+        <f t="shared" si="21"/>
+        <v>164</v>
+      </c>
+      <c r="C175" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="D175" s="84">
+        <v>36298</v>
+      </c>
+      <c r="E175" s="37">
+        <v>45843</v>
+      </c>
+      <c r="F175" s="82">
+        <v>3958000</v>
+      </c>
       <c r="G175" s="82"/>
       <c r="H175" s="46"/>
       <c r="I175" s="85"/>
@@ -11515,12 +14252,26 @@
       <c r="AE175" s="1"/>
       <c r="AF175" s="51"/>
     </row>
-    <row r="176" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B176" s="46"/>
-      <c r="C176" s="79"/>
-      <c r="D176" s="41"/>
-      <c r="E176" s="74"/>
-      <c r="F176" s="38"/>
+    <row r="176" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>87900085</v>
+      </c>
+      <c r="B176" s="46">
+        <f t="shared" si="21"/>
+        <v>165</v>
+      </c>
+      <c r="C176" s="79" t="s">
+        <v>204</v>
+      </c>
+      <c r="D176" s="41">
+        <v>36929</v>
+      </c>
+      <c r="E176" s="74">
+        <v>45843</v>
+      </c>
+      <c r="F176" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G176" s="38"/>
       <c r="H176" s="46"/>
       <c r="I176" s="85"/>
@@ -11546,12 +14297,26 @@
       <c r="AE176" s="1"/>
       <c r="AF176" s="51"/>
     </row>
-    <row r="177" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B177" s="46"/>
-      <c r="C177" s="79"/>
-      <c r="D177" s="41"/>
-      <c r="E177" s="74"/>
-      <c r="F177" s="38"/>
+    <row r="177" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>87900086</v>
+      </c>
+      <c r="B177" s="46">
+        <f t="shared" si="21"/>
+        <v>166</v>
+      </c>
+      <c r="C177" s="79" t="s">
+        <v>205</v>
+      </c>
+      <c r="D177" s="41">
+        <v>36861</v>
+      </c>
+      <c r="E177" s="74">
+        <v>45843</v>
+      </c>
+      <c r="F177" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G177" s="38"/>
       <c r="H177" s="46"/>
       <c r="I177" s="85"/>
@@ -11577,12 +14342,26 @@
       <c r="AE177" s="1"/>
       <c r="AF177" s="51"/>
     </row>
-    <row r="178" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B178" s="46"/>
-      <c r="C178" s="79"/>
-      <c r="D178" s="41"/>
-      <c r="E178" s="74"/>
-      <c r="F178" s="38"/>
+    <row r="178" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>87900087</v>
+      </c>
+      <c r="B178" s="46">
+        <f t="shared" si="21"/>
+        <v>167</v>
+      </c>
+      <c r="C178" s="79" t="s">
+        <v>206</v>
+      </c>
+      <c r="D178" s="41">
+        <v>36725</v>
+      </c>
+      <c r="E178" s="74">
+        <v>45843</v>
+      </c>
+      <c r="F178" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G178" s="38"/>
       <c r="H178" s="46"/>
       <c r="I178" s="85"/>
@@ -11608,12 +14387,26 @@
       <c r="AE178" s="1"/>
       <c r="AF178" s="51"/>
     </row>
-    <row r="179" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B179" s="46"/>
-      <c r="C179" s="79"/>
-      <c r="D179" s="41"/>
-      <c r="E179" s="74"/>
-      <c r="F179" s="38"/>
+    <row r="179" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>87900088</v>
+      </c>
+      <c r="B179" s="46">
+        <f t="shared" si="21"/>
+        <v>168</v>
+      </c>
+      <c r="C179" s="79" t="s">
+        <v>207</v>
+      </c>
+      <c r="D179" s="41">
+        <v>35500</v>
+      </c>
+      <c r="E179" s="74">
+        <v>45843</v>
+      </c>
+      <c r="F179" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G179" s="38"/>
       <c r="H179" s="46"/>
       <c r="I179" s="85"/>
@@ -11639,12 +14432,26 @@
       <c r="AE179" s="1"/>
       <c r="AF179" s="51"/>
     </row>
-    <row r="180" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B180" s="46"/>
-      <c r="C180" s="79"/>
-      <c r="D180" s="41"/>
-      <c r="E180" s="74"/>
-      <c r="F180" s="38"/>
+    <row r="180" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>87900090</v>
+      </c>
+      <c r="B180" s="46">
+        <f t="shared" si="21"/>
+        <v>169</v>
+      </c>
+      <c r="C180" s="79" t="s">
+        <v>208</v>
+      </c>
+      <c r="D180" s="41">
+        <v>35251</v>
+      </c>
+      <c r="E180" s="74">
+        <v>45843</v>
+      </c>
+      <c r="F180" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G180" s="38"/>
       <c r="H180" s="46"/>
       <c r="I180" s="85"/>
@@ -11670,12 +14477,26 @@
       <c r="AE180" s="1"/>
       <c r="AF180" s="51"/>
     </row>
-    <row r="181" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B181" s="46"/>
-      <c r="C181" s="79"/>
-      <c r="D181" s="41"/>
-      <c r="E181" s="74"/>
-      <c r="F181" s="38"/>
+    <row r="181" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A181" s="1">
+        <v>87900097</v>
+      </c>
+      <c r="B181" s="46">
+        <f t="shared" si="21"/>
+        <v>170</v>
+      </c>
+      <c r="C181" s="79" t="s">
+        <v>209</v>
+      </c>
+      <c r="D181" s="41">
+        <v>36981</v>
+      </c>
+      <c r="E181" s="74">
+        <v>45859</v>
+      </c>
+      <c r="F181" s="38">
+        <v>4058000</v>
+      </c>
       <c r="G181" s="38"/>
       <c r="H181" s="46"/>
       <c r="I181" s="90"/>
@@ -11701,12 +14522,26 @@
       <c r="AE181" s="1"/>
       <c r="AF181" s="51"/>
     </row>
-    <row r="182" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B182" s="46"/>
-      <c r="C182" s="79"/>
-      <c r="D182" s="41"/>
-      <c r="E182" s="74"/>
-      <c r="F182" s="38"/>
+    <row r="182" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>87900069</v>
+      </c>
+      <c r="B182" s="46">
+        <f t="shared" si="21"/>
+        <v>171</v>
+      </c>
+      <c r="C182" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="D182" s="41">
+        <v>36600</v>
+      </c>
+      <c r="E182" s="74">
+        <v>45859</v>
+      </c>
+      <c r="F182" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G182" s="38"/>
       <c r="H182" s="46"/>
       <c r="I182" s="85"/>
@@ -11732,12 +14567,26 @@
       <c r="AE182" s="1"/>
       <c r="AF182" s="51"/>
     </row>
-    <row r="183" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B183" s="46"/>
-      <c r="C183" s="79"/>
-      <c r="D183" s="41"/>
-      <c r="E183" s="74"/>
-      <c r="F183" s="38"/>
+    <row r="183" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>87900072</v>
+      </c>
+      <c r="B183" s="46">
+        <f t="shared" si="21"/>
+        <v>172</v>
+      </c>
+      <c r="C183" s="79" t="s">
+        <v>211</v>
+      </c>
+      <c r="D183" s="41">
+        <v>35825</v>
+      </c>
+      <c r="E183" s="74">
+        <v>45859</v>
+      </c>
+      <c r="F183" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G183" s="38"/>
       <c r="H183" s="46"/>
       <c r="I183" s="85"/>
@@ -11763,12 +14612,26 @@
       <c r="AE183" s="1"/>
       <c r="AF183" s="51"/>
     </row>
-    <row r="184" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B184" s="46"/>
-      <c r="C184" s="95"/>
-      <c r="D184" s="40"/>
-      <c r="E184" s="74"/>
-      <c r="F184" s="38"/>
+    <row r="184" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>87900073</v>
+      </c>
+      <c r="B184" s="46">
+        <f t="shared" si="21"/>
+        <v>173</v>
+      </c>
+      <c r="C184" s="95" t="s">
+        <v>212</v>
+      </c>
+      <c r="D184" s="40">
+        <v>38209</v>
+      </c>
+      <c r="E184" s="74">
+        <v>45859</v>
+      </c>
+      <c r="F184" s="38">
+        <v>3958000</v>
+      </c>
       <c r="G184" s="38"/>
       <c r="H184" s="46"/>
       <c r="I184" s="85"/>
@@ -11794,12 +14657,26 @@
       <c r="AE184" s="1"/>
       <c r="AF184" s="51"/>
     </row>
-    <row r="185" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B185" s="46"/>
-      <c r="C185" s="95"/>
-      <c r="D185" s="40"/>
-      <c r="E185" s="74"/>
-      <c r="F185" s="38"/>
+    <row r="185" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>87900096</v>
+      </c>
+      <c r="B185" s="46">
+        <f t="shared" si="21"/>
+        <v>174</v>
+      </c>
+      <c r="C185" s="95" t="s">
+        <v>213</v>
+      </c>
+      <c r="D185" s="40">
+        <v>34423</v>
+      </c>
+      <c r="E185" s="74">
+        <v>45859</v>
+      </c>
+      <c r="F185" s="38">
+        <v>4158000</v>
+      </c>
       <c r="G185" s="38"/>
       <c r="H185" s="46"/>
       <c r="I185" s="80"/>
@@ -11825,7 +14702,26 @@
       <c r="AE185" s="1"/>
       <c r="AF185" s="51"/>
     </row>
-    <row r="186" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A186" s="1">
+        <v>82400506</v>
+      </c>
+      <c r="B186" s="46">
+        <f t="shared" si="21"/>
+        <v>175</v>
+      </c>
+      <c r="C186" s="79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" s="41">
+        <v>35554</v>
+      </c>
+      <c r="E186" s="74">
+        <v>44779</v>
+      </c>
+      <c r="F186" s="38">
+        <v>5980000</v>
+      </c>
       <c r="G186" s="38"/>
       <c r="H186" s="46"/>
       <c r="I186" s="80"/>
@@ -11851,7 +14747,26 @@
       <c r="AE186" s="1"/>
       <c r="AF186" s="51"/>
     </row>
-    <row r="187" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A187" s="1">
+        <v>87900152</v>
+      </c>
+      <c r="B187" s="46">
+        <f t="shared" si="21"/>
+        <v>176</v>
+      </c>
+      <c r="C187" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="D187" s="40">
+        <v>34691</v>
+      </c>
+      <c r="E187" s="74">
+        <v>45852</v>
+      </c>
+      <c r="F187" s="38">
+        <v>4058000</v>
+      </c>
       <c r="G187" s="38"/>
       <c r="H187" s="46"/>
       <c r="I187" s="96"/>
@@ -11877,7 +14792,7 @@
       <c r="AE187" s="1"/>
       <c r="AF187" s="51"/>
     </row>
-    <row r="188" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B188" s="46"/>
       <c r="C188" s="46"/>
       <c r="D188" s="41"/>
@@ -11908,7 +14823,7 @@
       <c r="AE188" s="1"/>
       <c r="AF188" s="51"/>
     </row>
-    <row r="189" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B189" s="46"/>
       <c r="C189" s="46"/>
       <c r="D189" s="41"/>
@@ -11939,7 +14854,7 @@
       <c r="AE189" s="1"/>
       <c r="AF189" s="51"/>
     </row>
-    <row r="190" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B190" s="46"/>
       <c r="C190" s="46"/>
       <c r="D190" s="41"/>
@@ -11970,7 +14885,7 @@
       <c r="AE190" s="1"/>
       <c r="AF190" s="51"/>
     </row>
-    <row r="191" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B191" s="46"/>
       <c r="C191" s="46"/>
       <c r="D191" s="41"/>
@@ -11993,7 +14908,7 @@
       <c r="AE191" s="1"/>
       <c r="AF191" s="51"/>
     </row>
-    <row r="192" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B192" s="46"/>
       <c r="C192" s="46"/>
       <c r="D192" s="41"/>

--- a/data/file/template_karyawan.xlsx
+++ b/data/file/template_karyawan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aryax punya\2026\KKA VAB\Aplikasi\imbalan-pasca-kerja-app\data\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24F21B4-9E3B-4BC5-9E64-2FEF750E26F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B862BA0E-1F24-442D-BEF3-E71C7CABD2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F13F3C63-F4E3-4D7D-949D-333584CBF9CF}"/>
   </bookViews>
@@ -38,7 +38,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Arya Augusta:</t>
         </r>
@@ -47,7 +47,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 tidak ada tgl lahir jadi disamakan</t>
@@ -62,7 +62,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Arya Augusta:</t>
         </r>
@@ -71,7 +71,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 tidak ada tgl lahir jadi disamakan</t>
@@ -109,9 +109,6 @@
     <t>RSGN TAPI AKTIF</t>
   </si>
   <si>
-    <t>Aktif 2025</t>
-  </si>
-  <si>
     <t>Tgl Lahir</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
   </si>
   <si>
     <t>Gaji</t>
-  </si>
-  <si>
-    <t>Aktif 2024</t>
   </si>
   <si>
     <t>PBO</t>
@@ -164,9 +158,6 @@
   </si>
   <si>
     <t>PT LINTAS BAHARI NASIONAL</t>
-  </si>
-  <si>
-    <t>NOPEG</t>
   </si>
   <si>
     <t>LBN0898001</t>
@@ -351,6 +342,15 @@
   <si>
     <t>LBN1211001</t>
   </si>
+  <si>
+    <t>NIK</t>
+  </si>
+  <si>
+    <t>Aktif Tahun Ini</t>
+  </si>
+  <si>
+    <t>Aktif Tahun Lalu</t>
+  </si>
 </sst>
 </file>
 
@@ -362,7 +362,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -448,13 +448,13 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -758,8 +758,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="5" builtinId="3"/>
@@ -3585,10 +3585,10 @@
   <sheetData>
     <row r="1" spans="1:256" x14ac:dyDescent="0.3">
       <c r="E1" s="110" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
@@ -3865,78 +3865,78 @@
     </row>
     <row r="11" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A11" s="29" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="E11" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="F11" s="29" t="s">
         <v>10</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>11</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="18"/>
       <c r="J11" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="O11" s="29" t="s">
         <v>12</v>
-      </c>
-      <c r="K11" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="M11" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="N11" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="O11" s="29" t="s">
-        <v>14</v>
       </c>
       <c r="P11" s="29"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="T11" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="U11" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="V11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W11" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="S11" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="T11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="U11" s="29" t="s">
+      <c r="X11" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="V11" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="W11" s="29" t="s">
+      <c r="Y11" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="X11" s="31" t="s">
+      <c r="Z11" s="31" t="s">
         <v>18</v>
-      </c>
-      <c r="Y11" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z11" s="31" t="s">
-        <v>20</v>
       </c>
       <c r="AA11" s="29"/>
       <c r="AB11" s="32" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AC11" s="33"/>
       <c r="AD11" s="32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE11" s="2"/>
       <c r="AF11" s="2"/>
@@ -3944,12 +3944,12 @@
       <c r="AH11" s="29"/>
       <c r="AI11" s="29"/>
       <c r="AJ11" s="29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK11" s="34"/>
       <c r="AL11" s="35"/>
       <c r="AM11" s="29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AN11" s="29"/>
       <c r="AO11" s="29"/>
@@ -4171,13 +4171,13 @@
     </row>
     <row r="12" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D12" s="37">
         <v>27367</v>
@@ -4194,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K12" s="108">
         <v>27367</v>
@@ -4216,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="R12" s="36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="S12" s="40">
         <v>30068</v>
@@ -4231,7 +4231,7 @@
         <v>20000000</v>
       </c>
       <c r="W12" s="48" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X12" s="109"/>
       <c r="Y12" s="47"/>
@@ -4281,14 +4281,14 @@
     </row>
     <row r="13" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" s="46">
         <f t="shared" ref="B13:B39" si="1">B12+1</f>
         <v>2</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D13" s="37">
         <v>30990</v>
@@ -4306,7 +4306,7 @@
         <v>2</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K13" s="108">
         <v>30990</v>
@@ -4329,7 +4329,7 @@
         <v>2</v>
       </c>
       <c r="R13" s="36" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="S13" s="41">
         <v>32649</v>
@@ -4344,7 +4344,7 @@
         <v>23000000</v>
       </c>
       <c r="W13" s="48" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X13" s="109"/>
       <c r="Y13" s="47"/>
@@ -4394,14 +4394,14 @@
     </row>
     <row r="14" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B14" s="46">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D14" s="37">
         <v>36100</v>
@@ -4419,7 +4419,7 @@
         <v>3</v>
       </c>
       <c r="J14" s="39" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K14" s="108">
         <v>30068</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="R14" s="36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="S14" s="41">
         <v>34493</v>
@@ -4457,7 +4457,7 @@
         <v>10000000</v>
       </c>
       <c r="W14" s="48" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="X14" s="109"/>
       <c r="Y14" s="47"/>
@@ -4507,14 +4507,14 @@
     </row>
     <row r="15" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B15" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15" s="37">
         <v>33651</v>
@@ -4532,7 +4532,7 @@
         <v>4</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K15" s="108">
         <v>36100</v>
@@ -4601,14 +4601,14 @@
     </row>
     <row r="16" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B16" s="46">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D16" s="37">
         <v>35002</v>
@@ -4626,7 +4626,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="39" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K16" s="108">
         <v>35579</v>
@@ -4695,14 +4695,14 @@
     </row>
     <row r="17" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B17" s="46">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D17" s="37">
         <v>34867</v>
@@ -4720,7 +4720,7 @@
         <v>6</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K17" s="108">
         <v>28942</v>
@@ -4789,14 +4789,14 @@
     </row>
     <row r="18" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B18" s="46">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="37">
         <v>36354</v>
@@ -4814,7 +4814,7 @@
         <v>7</v>
       </c>
       <c r="J18" s="39" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K18" s="108">
         <v>27328</v>
@@ -4882,14 +4882,14 @@
     </row>
     <row r="19" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B19" s="46">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D19" s="37">
         <v>34454</v>
@@ -4907,7 +4907,7 @@
         <v>8</v>
       </c>
       <c r="J19" s="39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K19" s="108">
         <v>33188</v>
@@ -4975,14 +4975,14 @@
     </row>
     <row r="20" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B20" s="46">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D20" s="37">
         <v>37421</v>
@@ -5000,7 +5000,7 @@
         <v>9</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K20" s="108">
         <v>33716</v>
@@ -5068,14 +5068,14 @@
     </row>
     <row r="21" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B21" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D21" s="37">
         <v>37144</v>
@@ -5093,7 +5093,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K21" s="108">
         <v>36286</v>
@@ -5161,14 +5161,14 @@
     </row>
     <row r="22" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B22" s="46">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D22" s="37">
         <v>35579</v>
@@ -5186,7 +5186,7 @@
         <v>11</v>
       </c>
       <c r="J22" s="63" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K22" s="72">
         <v>35002</v>
@@ -5254,14 +5254,14 @@
     </row>
     <row r="23" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B23" s="46">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D23" s="37">
         <v>35940</v>
@@ -5279,7 +5279,7 @@
         <v>12</v>
       </c>
       <c r="J23" s="39" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K23" s="108">
         <v>32649</v>
@@ -5562,14 +5562,14 @@
     </row>
     <row r="24" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B24" s="46">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D24" s="37">
         <v>35551</v>
@@ -5587,7 +5587,7 @@
         <v>13</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K24" s="108">
         <v>34493</v>
@@ -5655,14 +5655,14 @@
     </row>
     <row r="25" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B25" s="46">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D25" s="37">
         <v>27061</v>
@@ -5680,7 +5680,7 @@
         <v>14</v>
       </c>
       <c r="J25" s="39" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K25" s="108">
         <v>36354</v>
@@ -5748,14 +5748,14 @@
     </row>
     <row r="26" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B26" s="46">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D26" s="37">
         <v>32110</v>
@@ -5773,7 +5773,7 @@
         <v>15</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K26" s="108">
         <v>34867</v>
@@ -5841,14 +5841,14 @@
     </row>
     <row r="27" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B27" s="46">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D27" s="37">
         <v>37722</v>
@@ -5866,7 +5866,7 @@
         <v>16</v>
       </c>
       <c r="J27" s="39" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K27" s="108">
         <v>34454</v>
@@ -5934,14 +5934,14 @@
     </row>
     <row r="28" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B28" s="46">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D28" s="37">
         <v>24925</v>
@@ -5959,7 +5959,7 @@
         <v>17</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K28" s="108">
         <v>37421</v>
@@ -6027,14 +6027,14 @@
     </row>
     <row r="29" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B29" s="46">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D29" s="37">
         <v>33121</v>
@@ -6052,7 +6052,7 @@
         <v>18</v>
       </c>
       <c r="J29" s="39" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K29" s="108">
         <v>37144</v>
@@ -6120,14 +6120,14 @@
     </row>
     <row r="30" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B30" s="46">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D30" s="37">
         <v>36307</v>
@@ -6145,7 +6145,7 @@
         <v>19</v>
       </c>
       <c r="J30" s="63" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K30" s="72">
         <v>27061</v>
@@ -6213,14 +6213,14 @@
     </row>
     <row r="31" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B31" s="46">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D31" s="37">
         <v>28942</v>
@@ -6238,7 +6238,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="63" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K31" s="72">
         <v>32110</v>
@@ -6306,14 +6306,14 @@
     </row>
     <row r="32" spans="1:256" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B32" s="46">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D32" s="37">
         <v>35824</v>
@@ -6331,7 +6331,7 @@
         <v>21</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K32" s="108">
         <v>24925</v>
@@ -6399,14 +6399,14 @@
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B33" s="46">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D33" s="37">
         <v>27328</v>
@@ -6424,7 +6424,7 @@
         <v>22</v>
       </c>
       <c r="J33" s="63" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K33" s="72">
         <v>33121</v>
@@ -6492,14 +6492,14 @@
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B34" s="46">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D34" s="37">
         <v>36151</v>
@@ -6517,7 +6517,7 @@
         <v>23</v>
       </c>
       <c r="J34" s="63" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K34" s="72">
         <v>32157</v>
@@ -6560,14 +6560,14 @@
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B35" s="46">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D35" s="37">
         <v>35601</v>
@@ -6613,14 +6613,14 @@
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B36" s="46">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D36" s="37">
         <v>33716</v>
@@ -6667,14 +6667,14 @@
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B37" s="46">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D37" s="37">
         <v>33188</v>
@@ -6721,14 +6721,14 @@
     </row>
     <row r="38" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B38" s="46">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D38" s="37">
         <v>36286</v>
@@ -6775,14 +6775,14 @@
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B39" s="46">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D39" s="37">
         <v>32157</v>
